--- a/Data/IP_ThePresident.xlsx
+++ b/Data/IP_ThePresident.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,176 +472,176 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Who is the constitutional head of India?</t>
+          <t>Which article deals with the election of the President?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Article 52</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 54</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Article 61</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 54</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>The President is the nominal executive head.</t>
+          <t>It provides the procedure.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The President of India is elected by</t>
+          <t>The President can appoint how many members to Rajya Sabha?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>People directly</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Lok Sabha only</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rajya Sabha only</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Electoral college</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Electoral college</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Includes MPs and MLAs.</t>
+          <t>As per Article 80.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>What is the term of office of the President?</t>
+          <t>President gives his resignation to</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Vice-President</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Till death</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Vice-President</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Mentioned in Article 56.</t>
+          <t>As per Article 56.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which Article deals with the election of the President?</t>
+          <t>Which President was also a freedom fighter and teacher?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Article 52</t>
+          <t>Pranab Mukherjee</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Article 54</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Sarvepalli Radhakrishnan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Fakhruddin Ali Ahmed</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Article 54</t>
+          <t>Sarvepalli Radhakrishnan</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Describes election process.</t>
+          <t>2nd President and philosopher.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Who administers oath to the President?</t>
+          <t>In case of vacancy, who acts as President?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -656,2427 +656,2415 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Vice-President</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>As per Article 60.</t>
+          <t>Acts till new President elected.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which one is not a qualification for becoming President?</t>
+          <t>President acts on the aid and advice of</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indian citizen</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Completed 35 years</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Member of Parliament</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Qualified to be Lok Sabha member</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Member of Parliament</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Only need eligibility to become one.</t>
+          <t>As per Article 74.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Minimum age for President of India is</t>
+          <t>During President's Rule, the President acts through</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Same as for Governor and Vice President.</t>
+          <t>He governs on behalf of President.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>President is elected by</t>
+          <t>Can President reject advice of Council of Ministers?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>First-past-the-post</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Proportional representation</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Simple majority</t>
+          <t>Yes, in all cases</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lottery system</t>
+          <t>Only during emergency</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Proportional representation</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Single transferable vote.</t>
+          <t>Bound to act as per Article 74 (after 42nd Amendment).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Who can remove the President before term ends?</t>
+          <t>What majority is required for impeachment of President?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Simple</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Absolute</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>2/3rd of total membership</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>2/3rd of members present and voting</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>2/3rd of total membership</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Through impeachment process.</t>
+          <t>Of both Houses.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Impeachment of the President is mentioned in</t>
+          <t>President is part of</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Article 61</t>
+          <t>Executive only</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Article 54</t>
+          <t>Parliament only</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Judiciary only</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Article 61</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Details process and majority needed.</t>
+          <t>Along with Lok Sabha and Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Can a President be re-elected?</t>
+          <t>President's assent to a bill converts it into</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Act</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Only once</t>
+          <t>Ordinance</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yes, any number of times</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Only twice</t>
+          <t>Law</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Yes, any number of times</t>
+          <t>Act</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>No limit on re-election.</t>
+          <t>Law comes into force after assent.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>In case of vacancy, who acts as President?</t>
+          <t>President’s address to the Parliament is under</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Article 72</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Article 86</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Vice-President</t>
+          <t>Article 87</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>Article 89</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Vice-President</t>
+          <t>Article 87</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Acts till new President elected.</t>
+          <t>At the beginning of first session each year.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>President gives his resignation to</t>
+          <t>Which body does not participate in Presidential election?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vice-President</t>
+          <t>State Assemblies</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>Legislative Councils</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Vice-President</t>
+          <t>Legislative Councils</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>As per Article 56.</t>
+          <t>Only elected MLAs and MPs vote.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>What is the President's veto power called?</t>
+          <t>Who was the first President of India?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Judicial veto</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Executive veto</t>
+          <t>S. Radhakrishnan</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Legislative veto</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pocket veto</t>
+          <t>V.V. Giri</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pocket veto</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Where President takes no action on a bill.</t>
+          <t>Only President to serve 2 full terms.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which type of bill requires President’s prior recommendation?</t>
+          <t>Which Article deals with the election of the President?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finance Bill</t>
+          <t>Article 52</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Money Bill</t>
+          <t>Article 54</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ordinary Bill</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Private Bill</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Money Bill</t>
+          <t>Article 54</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Introduced only with President's approval.</t>
+          <t>Describes election process.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>President can dissolve Lok Sabha on advice of</t>
+          <t>President’s salary is decided by</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Headed by Prime Minister.</t>
+          <t>As per Article 125.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which emergency needs written recommendation of Cabinet to President?</t>
+          <t>Who decides disputes regarding Presidential elections?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>President's Rule</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>National Emergency</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Financial Emergency</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>National Emergency</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>As per 44th Amendment.</t>
+          <t>Under Article 71.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>President can declare Financial Emergency under</t>
+          <t>Which of these is not appointed by the President?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Article 352</t>
+          <t>Comptroller and Auditor General</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>Chief Election Commissioner</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Article 360</t>
+          <t>Chief Minister</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Article 370</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Article 360</t>
+          <t>Chief Minister</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>If financial stability is threatened.</t>
+          <t>Appointed by Governor.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ordinance-making power of President is under</t>
+          <t>Who can initiate impeachment of the President?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Article 123</t>
+          <t>Only Lok Sabha</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Only Rajya Sabha</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>Either House</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Article 123</t>
+          <t>Either House</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Allows President to make laws when Parliament not in session.</t>
+          <t>With required majority.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>President acts on aid and advice of</t>
+          <t>President’s election can be challenged in</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>Supreme Court</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>High Court</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Election Commission</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>Lok Sabha</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Judiciary</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Council of Ministers</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Rajya Sabha</t>
-        </is>
-      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Article 74 mandates this.</t>
+          <t>As per Article 71.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Who appoints the Prime Minister of India?</t>
+          <t>The first President of Independent India was</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Vice-President</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Sarvepalli Radhakrishnan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Generally the leader of majority.</t>
+          <t>Served from 1950 to 1962.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>President's assent to a bill converts it into</t>
+          <t>The President is elected by</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Act</t>
+          <t>People directly</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ordinance</t>
+          <t>MLAs only</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>MPs only</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Law</t>
+          <t>Electoral college</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Act</t>
+          <t>Electoral college</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Law comes into force after assent.</t>
+          <t>Includes elected MPs and MLAs.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>President is part of</t>
+          <t>President can dissolve Lok Sabha on advice of</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Executive only</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Parliament only</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Judiciary only</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Along with Lok Sabha and Rajya Sabha.</t>
+          <t>Headed by Prime Minister.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>President nominates how many members to Rajya Sabha?</t>
+          <t>Who administers the oath of office to the President?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Experts in art, literature, science &amp; social service.</t>
+          <t>As per tradition and Article 60.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which of these is not a discretionary power of President?</t>
+          <t>What is the term of office of the President?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sending back advice</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Appointing PM</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dismissing CM</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pocket veto</t>
+          <t>Till death</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dismissing CM</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>President must act on aid and advice.</t>
+          <t>Mentioned in Article 56.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Who decides disputes regarding Presidential elections?</t>
+          <t>President’s rule is imposed under</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Article 352</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 360</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Article 370</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Under Article 71.</t>
+          <t>When state machinery fails.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which amendment made it mandatory for the Cabinet to advise the President in writing?</t>
+          <t>In which case did Supreme Court define Presidential powers under Article 74?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Golaknath Case</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Kesavananda Bharati Case</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>S.R. Bommai Case</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>73rd Amendment</t>
+          <t>Shamsher Singh Case</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Shamsher Singh Case</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Added to ensure accountability.</t>
+          <t>Clarified "aid and advice".</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>President can appoint which of the following?</t>
+          <t>The President of India is elected by</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>People directly</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Lok Sabha only</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>Rajya Sabha only</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Electoral college</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Electoral college</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>President appoints several constitutional authorities.</t>
+          <t>Includes MPs and MLAs.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which of the following is true about the President’s ordinance power?</t>
+          <t>Term of office of the President is</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>It can be issued anytime</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>It is equal to law</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>It is permanent</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>It bypasses Parliament</t>
+          <t>Until Parliament decides</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>It is equal to law</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>But only temporary till Parliament acts.</t>
+          <t>Can be re-elected.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>When can the President use veto power?</t>
+          <t>Which President served as Vice President before becoming President?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Any bill</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Money bill</t>
+          <t>Sarvepalli Radhakrishnan</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Finance bill</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Budget bill</t>
+          <t>Pranab Mukherjee</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Any bill</t>
+          <t>Sarvepalli Radhakrishnan</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Except money bill in some cases.</t>
+          <t>Vice President from 1952–62.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>President can return a bill to Parliament</t>
+          <t>President’s power to grant pardon is under</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Any number of times</t>
+          <t>Article 72</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Only once</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Twice</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Only once</t>
+          <t>Article 72</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>If passed again, must give assent.</t>
+          <t>Covers pardon, reprieve, respite etc.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>How is value of vote of an MLA in Presidential election determined?</t>
+          <t>What is the maximum gap allowed between two sessions of Parliament?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Equal to MP</t>
+          <t>3 months</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Based on population</t>
+          <t>4 months</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>One vote only</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Random allotment</t>
+          <t>9 months</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Based on population</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Population to MLA ratio of the state.</t>
+          <t>As per Article 85.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>What majority is required for impeachment of President?</t>
+          <t>In case of dispute in Presidential election, which body decides?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Simple</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Absolute</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2/3rd of total membership</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2/3rd of members present and voting</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2/3rd of total membership</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Of both Houses.</t>
+          <t>As per Article 71.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>President’s election can be challenged in</t>
+          <t>Who is the constitutional head of India?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>High Court</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>As per Article 71.</t>
+          <t>The President is the nominal executive head.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which of these is not appointed by the President?</t>
+          <t>Who assists the President in their official duties?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Comptroller and Auditor General</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Chief Election Commissioner</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chief Minister</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Cabinet Secretary</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chief Minister</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Appointed by Governor.</t>
+          <t>Headed by Prime Minister.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which body does not participate in Presidential election?</t>
+          <t>Can President's salary be reduced during emergency?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>State Assemblies</t>
+          <t>Only by Parliament</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Legislative Councils</t>
+          <t>Only by Supreme Court</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Legislative Councils</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Only elected MLAs and MPs vote.</t>
+          <t>Under Financial Emergency (Article 360).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Who was the first President of India?</t>
+          <t>When can the President use veto power?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>Any bill</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>S. Radhakrishnan</t>
+          <t>Money bill</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Finance bill</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>V.V. Giri</t>
+          <t>Budget bill</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>Any bill</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Only President to serve 2 full terms.</t>
+          <t>Except money bill in some cases.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Who was the first woman President of India?</t>
+          <t>Impeachment of the President is mentioned in</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Article 61</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Article 54</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sushma Swaraj</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Article 61</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Elected in 2007.</t>
+          <t>Details process and majority needed.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which President served during Emergency (1975)?</t>
+          <t>Which body conducts Presidential elections?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Zail Singh</t>
+          <t>Election Commission of India</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fakhruddin Ali Ahmed</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fakhruddin Ali Ahmed</t>
+          <t>Election Commission of India</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Signed emergency proclamation in 1975.</t>
+          <t>As per Article 324.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Who can initiate impeachment of the President?</t>
+          <t>Who was the first woman President of India?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Only Lok Sabha</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Only Rajya Sabha</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Either House</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Sushma Swaraj</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Either House</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>With required majority.</t>
+          <t>Elected in 2007.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>President’s power to grant pardon is under</t>
+          <t>What is the President's veto power called?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Article 72</t>
+          <t>Judicial veto</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Executive veto</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>Legislative veto</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>Pocket veto</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Article 72</t>
+          <t>Pocket veto</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Covers pardon, reprieve, respite etc.</t>
+          <t>Where President takes no action on a bill.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which of these is NOT a judicial power of the President?</t>
+          <t>Which President served two terms?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pardon</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Reprieve</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Remission</t>
+          <t>R. Venkataraman</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Review of judgment</t>
+          <t>Giani Zail Singh</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Review of judgment</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Done only by courts.</t>
+          <t>Only President to serve two terms.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The President can summon Parliament under</t>
+          <t>During vacancy in President's office, election must be held within</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Article 85</t>
+          <t>1 month</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Article 123</t>
+          <t>2 months</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Article 324</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Article 85</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>President summons and prorogues Parliament.</t>
+          <t>As per Article 62.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>President’s rule is imposed under</t>
+          <t>Who appoints the Prime Minister of India?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Article 352</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>Vice-President</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Article 360</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Article 370</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>When state machinery fails.</t>
+          <t>Generally the leader of majority.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Who assists the President in their official duties?</t>
+          <t>The President is the part of</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cabinet Secretary</t>
+          <t>All of these</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Headed by Prime Minister.</t>
+          <t>As per Article 53.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Can the President attend Parliamentary sessions?</t>
+          <t>Which President was known as the 'Missile Man of India'?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Yes, always</t>
+          <t>R. Venkataraman</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Yes, only inaugural</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Yes, but without voting</t>
+          <t>Pranab Mukherjee</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Yes, only inaugural</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>President addresses first session each year.</t>
+          <t>11th President, a scientist.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>During vacancy in President's office, election must be held within</t>
+          <t>How many times can one person be elected as President?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1 month</t>
+          <t>Once</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2 months</t>
+          <t>Twice</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Thrice</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>Any number of times</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Any number of times</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>As per Article 62.</t>
+          <t>No limit in Constitution.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>President’s salary is decided by</t>
+          <t>President can declare Financial Emergency under</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Article 352</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Article 360</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Article 370</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 360</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>As per Article 125.</t>
+          <t>If financial stability is threatened.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Who was President during Indo-Pak war of 1971?</t>
+          <t>Who was the first Sikh President of India?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Giani Zail Singh</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>V.V. Giri</t>
+          <t>KR Narayanan</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>R. Venkataraman</t>
+          <t>Pranab Mukherjee</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>V.V. Giri</t>
+          <t>Giani Zail Singh</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>In office during war.</t>
+          <t>Served from 1982–87.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>President can dissolve Lok Sabha under</t>
+          <t>President can return a bill to Parliament</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Article 85</t>
+          <t>Any number of times</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Article 75</t>
+          <t>Only once</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Article 352</t>
+          <t>Twice</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Article 368</t>
+          <t>Never</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Article 85</t>
+          <t>Only once</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>When advised by Council of Ministers.</t>
+          <t>If passed again, must give assent.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>In case of President's death or resignation, who acts as President?</t>
+          <t>Which house introduces impeachment charges?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Only Lok Sabha</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Only Rajya Sabha</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Any House</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Any House</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>As per Article 65.</t>
+          <t>But with special majority.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>President can declare financial emergency under</t>
+          <t>Which emergency needs written recommendation of Cabinet to President?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Article 352</t>
+          <t>President's Rule</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>National Emergency</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Article 360</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Article 365</t>
-        </is>
-      </c>
+          <t>Financial Emergency</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Article 360</t>
+          <t>National Emergency</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>When financial stability is threatened.</t>
+          <t>As per 44th Amendment.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Minimum age to contest Presidential election is</t>
+          <t>Who was President during Indo-Pak war of 1971?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>30 years</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>35 years</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>40 years</t>
+          <t>V.V. Giri</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>25 years</t>
+          <t>R. Venkataraman</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>35 years</t>
+          <t>V.V. Giri</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>As per Article 58.</t>
+          <t>In office during war.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which article deals with the election of the President?</t>
+          <t>Which President started ‘Rashtrapati Bhavan Darshan’?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Article 52</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Article 54</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Article 61</t>
+          <t>R. Venkataraman</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Article 54</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>It provides the procedure.</t>
+          <t>To promote public interaction.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>The President is the part of</t>
+          <t>The first Dalit President of India was</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>KR Narayanan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>R Venkataraman</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Giani Zail Singh</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>All of these</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>KR Narayanan</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>As per Article 53.</t>
+          <t>10th President of India.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which one is a discretionary power of the President?</t>
+          <t>The salary and allowances of the President are decided by</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dissolving Lok Sabha</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Appointing PM in hung Parliament</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ordinance</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pardoning</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Appointing PM in hung Parliament</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>When no party has clear majority.</t>
+          <t>As per Article 59.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Term of office of the President is</t>
+          <t>Who was the first President to be elected unopposed?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Neelam Sanjiva Reddy</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Until Parliament decides</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Neelam Sanjiva Reddy</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Can be re-elected.</t>
+          <t>Elected unopposed in 1977.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which President was known as the 'Missile Man of India'?</t>
+          <t>Which of these is not a discretionary power of President?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Sending back advice</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>R. Venkataraman</t>
+          <t>Appointing PM</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Dismissing CM</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pranab Mukherjee</t>
+          <t>Pocket veto</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Dismissing CM</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>11th President, a scientist.</t>
+          <t>President must act on aid and advice.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Who administers the oath of office to the President?</t>
+          <t>Can a person be President and member of Parliament at the same time?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Only if nominated</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>Only if Speaker</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>As per tradition and Article 60.</t>
+          <t>Cannot hold both offices.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>President’s address to the Parliament is under</t>
+          <t>Which type of bill requires President’s prior recommendation?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Article 72</t>
+          <t>Finance Bill</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Article 86</t>
+          <t>Money Bill</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Article 87</t>
+          <t>Ordinary Bill</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Article 89</t>
+          <t>Private Bill</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Article 87</t>
+          <t>Money Bill</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>At the beginning of first session each year.</t>
+          <t>Introduced only with President's approval.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which President served for the shortest term?</t>
+          <t>Which of these is NOT a judicial power of the President?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>Pardon</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Reprieve</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fakhruddin Ali Ahmed</t>
+          <t>Remission</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pranab Mukherjee</t>
+          <t>Review of judgment</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Review of judgment</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Died during term in 1969.</t>
+          <t>Done only by courts.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The first Dalit President of India was</t>
+          <t>President can declare financial emergency under</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>KR Narayanan</t>
+          <t>Article 352</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>R Venkataraman</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Giani Zail Singh</t>
+          <t>Article 360</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Article 365</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>KR Narayanan</t>
+          <t>Article 360</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>10th President of India.</t>
+          <t>When financial stability is threatened.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>President gives resignation to</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Vice President</t>
-        </is>
-      </c>
+          <t>Which President faced impeachment motion?</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Vice President</t>
-        </is>
-      </c>
+          <t>Rajendra Prasad</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>As per Article 56.</t>
+          <t>No Indian President has been impeached.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Can President be re-elected?</t>
+          <t>President may not return which type of bill?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Yes, only once</t>
+          <t>Ordinary Bill</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Yes, any number of times</t>
+          <t>Money Bill</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Constitutional Amendment Bill</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Only after 5 years gap</t>
+          <t>Finance Bill</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Yes, any number of times</t>
+          <t>Money Bill</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>No restriction in Constitution.</t>
+          <t>No power to return it.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which body conducts Presidential elections?</t>
+          <t>President can appoint which of the following?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Election Commission of India</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Election Commission of India</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>As per Article 324.</t>
+          <t>President appoints several constitutional authorities.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which President started ‘Rashtrapati Bhavan Darshan’?</t>
+          <t>Which President served during Emergency (1975)?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3086,1387 +3074,1387 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>Zail Singh</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Fakhruddin Ali Ahmed</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t>APJ Abdul Kalam</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>R. Venkataraman</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Pratibha Patil</t>
-        </is>
-      </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Fakhruddin Ali Ahmed</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>To promote public interaction.</t>
+          <t>Signed emergency proclamation in 1975.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>President’s signature is required on</t>
+          <t>Which one is not a qualification for becoming President?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Money Bills</t>
+          <t>Indian citizen</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Ordinances</t>
+          <t>Completed 35 years</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Proclamations of Emergency</t>
+          <t>Member of Parliament</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>All of these</t>
+          <t>Qualified to be Lok Sabha member</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>All of these</t>
+          <t>Member of Parliament</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>As head of state.</t>
+          <t>Only need eligibility to become one.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>President may not return which type of bill?</t>
+          <t>Can President dissolve Rajya Sabha?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ordinary Bill</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Money Bill</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Constitutional Amendment Bill</t>
+          <t>Only with Supreme Court advice</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Finance Bill</t>
+          <t>Only during Emergency</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Money Bill</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>No power to return it.</t>
+          <t>Rajya Sabha is a permanent house.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which house introduces impeachment charges?</t>
+          <t>Who is the supreme commander of the armed forces?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Only Lok Sabha</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Only Rajya Sabha</t>
+          <t>Defense Minister</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Any House</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Chief of Defense Staff</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Any House</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>But with special majority.</t>
+          <t>As per Article 53.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which is not a legislative power of the President?</t>
+          <t>How is value of vote of an MLA in Presidential election determined?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Summon Parliament</t>
+          <t>Equal to MP</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Dissolve Lok Sabha</t>
+          <t>Based on population</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Give assent to bills</t>
+          <t>One vote only</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vote in Parliament</t>
+          <t>Random allotment</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Vote in Parliament</t>
+          <t>Based on population</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>President doesn't vote.</t>
+          <t>Population to MLA ratio of the state.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>What is the maximum gap allowed between two sessions of Parliament?</t>
+          <t>President nominates how many members to Rajya Sabha?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>3 months</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>4 months</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>9 months</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>As per Article 85.</t>
+          <t>Experts in art, literature, science &amp; social service.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Who was the first President to be elected unopposed?</t>
+          <t>Who can remove the President before term ends?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Neelam Sanjiva Reddy</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neelam Sanjiva Reddy</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Elected unopposed in 1977.</t>
+          <t>Through impeachment process.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>President acts on the aid and advice of</t>
+          <t>Which President served for the shortest term?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Fakhruddin Ali Ahmed</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Pranab Mukherjee</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>As per Article 74.</t>
+          <t>Died during term in 1969.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which President was also a freedom fighter and teacher?</t>
+          <t>President gives resignation to</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Pranab Mukherjee</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sarvepalli Radhakrishnan</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fakhruddin Ali Ahmed</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sarvepalli Radhakrishnan</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2nd President and philosopher.</t>
+          <t>As per Article 56.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Who can remove the President for violation of the Constitution?</t>
+          <t>Who was acting President after Dr. Zakir Hussain’s death?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>VV Giri</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Neelam Sanjiva Reddy</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Mohammad Hidayatullah</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Giani Zail Singh</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Mohammad Hidayatullah</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Through impeachment process.</t>
+          <t>As Chief Justice of India.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The salary and allowances of the President are decided by</t>
+          <t>President acts on aid and advice of</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>As per Article 59.</t>
+          <t>Article 74 mandates this.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>The first woman to contest Presidential election in India was</t>
+          <t>Which article states that executive power is vested in President?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Article 53</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Meira Kumar</t>
+          <t>Article 60</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Article 70</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Subhadra Joshi</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Subhadra Joshi</t>
+          <t>Article 53</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Contested in 1967.</t>
+          <t>Power of Union is vested in President.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The President can appoint how many members to Rajya Sabha?</t>
+          <t>Which Article empowers President to grant pardons?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Article 60</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Article 72</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>Article 102</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Article 72</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>As per Article 80.</t>
+          <t>Includes pardon, reprieve, respite, remission.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>In case of dispute in Presidential election, which body decides?</t>
+          <t>Ordinance-making power of President is under</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 123</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Article 123</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>As per Article 71.</t>
+          <t>Allows President to make laws when Parliament not in session.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>President can issue ordinances under</t>
+          <t>If the post of Vice President is vacant, who acts as Vice President?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Article 352</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Article 123</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>No one</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Article 123</t>
+          <t>No one</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>When Parliament is not in session.</t>
+          <t>President’s role continues as is.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Who is the supreme commander of the armed forces?</t>
+          <t>Can the President attend Parliamentary sessions?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Defense Minister</t>
+          <t>Yes, always</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Yes, only inaugural</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Chief of Defense Staff</t>
+          <t>Yes, but without voting</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Yes, only inaugural</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>As per Article 53.</t>
+          <t>President addresses first session each year.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Which Article empowers President to grant pardons?</t>
+          <t>President is elected by</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Article 60</t>
+          <t>First-past-the-post</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Article 72</t>
+          <t>Proportional representation</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Simple majority</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Article 102</t>
+          <t>Lottery system</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Article 72</t>
+          <t>Proportional representation</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Includes pardon, reprieve, respite, remission.</t>
+          <t>Single transferable vote.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Which President served as Vice President before becoming President?</t>
+          <t>Can a President be re-elected?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Sarvepalli Radhakrishnan</t>
+          <t>Only once</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Yes, any number of times</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pranab Mukherjee</t>
+          <t>Only twice</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sarvepalli Radhakrishnan</t>
+          <t>Yes, any number of times</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Vice President from 1952–62.</t>
+          <t>No limit on re-election.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>In which case did Supreme Court define Presidential powers under Article 74?</t>
+          <t>Minimum age to contest Presidential election is</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Golaknath Case</t>
+          <t>30 years</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati Case</t>
+          <t>35 years</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>S.R. Bommai Case</t>
+          <t>40 years</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Shamsher Singh Case</t>
+          <t>25 years</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Shamsher Singh Case</t>
+          <t>35 years</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Clarified "aid and advice".</t>
+          <t>As per Article 58.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Can President reject advice of Council of Ministers?</t>
+          <t>The President can summon Parliament under</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Article 85</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Article 123</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Yes, in all cases</t>
+          <t>Article 324</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Only during emergency</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Article 85</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Bound to act as per Article 74 (after 42nd Amendment).</t>
+          <t>President summons and prorogues Parliament.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>The President is elected by</t>
+          <t>Can President be re-elected?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>People directly</t>
+          <t>Yes, only once</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>MLAs only</t>
+          <t>Yes, any number of times</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>MPs only</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Electoral college</t>
+          <t>Only after 5 years gap</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Electoral college</t>
+          <t>Yes, any number of times</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Includes elected MPs and MLAs.</t>
+          <t>No restriction in Constitution.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>During President's Rule, the President acts through</t>
+          <t>In case of President's death or resignation, who acts as President?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>He governs on behalf of President.</t>
+          <t>As per Article 65.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>How many times can one person be elected as President?</t>
+          <t>Which President had the shortest tenure before resignation?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Once</t>
+          <t>VV Giri</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Twice</t>
+          <t>R. Venkataraman</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Thrice</t>
+          <t>Neelam Sanjiva Reddy</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Any number of times</t>
+          <t>Dr. Zakir Hussain</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Any number of times</t>
+          <t>VV Giri</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>No limit in Constitution.</t>
+          <t>As acting President before election.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>If the post of Vice President is vacant, who acts as Vice President?</t>
+          <t>Who can remove the President for violation of the Constitution?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>No one</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>No one</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>President’s role continues as is.</t>
+          <t>Through impeachment process.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Can a person be President and member of Parliament at the same time?</t>
+          <t>Minimum age for President of India is</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Only if nominated</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Only if Speaker</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Cannot hold both offices.</t>
+          <t>Same as for Governor and Vice President.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>91</v>
+        <v>27</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Who was acting President after Dr. Zakir Hussain’s death?</t>
+          <t>Which amendment made it mandatory for the Cabinet to advise the President in writing?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>VV Giri</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Neelam Sanjiva Reddy</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mohammad Hidayatullah</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Giani Zail Singh</t>
+          <t>73rd Amendment</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Mohammad Hidayatullah</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>As Chief Justice of India.</t>
+          <t>Added to ensure accountability.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Which President had the shortest tenure before resignation?</t>
+          <t>Which one is a discretionary power of the President?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>VV Giri</t>
+          <t>Dissolving Lok Sabha</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>R. Venkataraman</t>
+          <t>Appointing PM in hung Parliament</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Neelam Sanjiva Reddy</t>
+          <t>Ordinance</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dr. Zakir Hussain</t>
+          <t>Pardoning</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>VV Giri</t>
+          <t>Appointing PM in hung Parliament</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>As acting President before election.</t>
+          <t>When no party has clear majority.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Can President dissolve Rajya Sabha?</t>
+          <t>Which is not a legislative power of the President?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Summon Parliament</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Dissolve Lok Sabha</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Only with Supreme Court advice</t>
+          <t>Give assent to bills</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Only during Emergency</t>
+          <t>Vote in Parliament</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Vote in Parliament</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Rajya Sabha is a permanent house.</t>
+          <t>President doesn't vote.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which President faced impeachment motion?</t>
+          <t>President can issue ordinances under</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Article 352</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Article 123</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Article 123</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>No Indian President has been impeached.</t>
+          <t>When Parliament is not in session.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Who was the first Sikh President of India?</t>
+          <t>The President can promulgate ordinances when</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Parliament is in session</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Giani Zail Singh</t>
+          <t>Only Lok Sabha is not in session</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>KR Narayanan</t>
+          <t>Parliament is not in session</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pranab Mukherjee</t>
+          <t>PM suggests</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Giani Zail Singh</t>
+          <t>Parliament is not in session</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Served from 1982–87.</t>
+          <t>Under Article 123.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>The President can promulgate ordinances when</t>
+          <t>The first woman to contest Presidential election in India was</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Parliament is in session</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Only Lok Sabha is not in session</t>
+          <t>Meira Kumar</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Parliament is not in session</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>PM suggests</t>
+          <t>Subhadra Joshi</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Parliament is not in session</t>
+          <t>Subhadra Joshi</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Under Article 123.</t>
+          <t>Contested in 1967.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Which article states that executive power is vested in President?</t>
+          <t>Which of the following is true about the President’s ordinance power?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Article 53</t>
+          <t>It can be issued anytime</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Article 60</t>
+          <t>It is equal to law</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Article 70</t>
+          <t>It is permanent</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>It bypasses Parliament</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Article 53</t>
+          <t>It is equal to law</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Power of Union is vested in President.</t>
+          <t>But only temporary till Parliament acts.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>The first President of Independent India was</t>
+          <t>President’s signature is required on</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Money Bills</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>Ordinances</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sarvepalli Radhakrishnan</t>
+          <t>Proclamations of Emergency</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>All of these</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>All of these</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Served from 1950 to 1962.</t>
+          <t>As head of state.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Which President served two terms?</t>
+          <t>President can dissolve Lok Sabha under</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Article 85</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>Article 75</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>R. Venkataraman</t>
+          <t>Article 352</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Giani Zail Singh</t>
+          <t>Article 368</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>Article 85</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Only President to serve two terms.</t>
+          <t>When advised by Council of Ministers.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Can President's salary be reduced during emergency?</t>
+          <t>Who administers oath to the President?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Only by Parliament</t>
+          <t>Vice-President</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Only by Supreme Court</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Under Financial Emergency (Article 360).</t>
+          <t>As per Article 60.</t>
         </is>
       </c>
     </row>

--- a/Data/IP_ThePresident.xlsx
+++ b/Data/IP_ThePresident.xlsx
@@ -472,176 +472,176 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which article deals with the election of the President?</t>
+          <t>President is part of</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Article 52</t>
+          <t>Executive only</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Article 54</t>
+          <t>Parliament only</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Article 61</t>
+          <t>Judiciary only</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Article 54</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>It provides the procedure.</t>
+          <t>Along with Lok Sabha and Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The President can appoint how many members to Rajya Sabha?</t>
+          <t>What majority is required for impeachment of President?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Simple</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Absolute</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2/3rd of total membership</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2/3rd of members present and voting</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2/3rd of total membership</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>As per Article 80.</t>
+          <t>Of both Houses.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>President gives his resignation to</t>
+          <t>Can President reject advice of Council of Ministers?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vice-President</t>
+          <t>Yes, in all cases</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>Only during emergency</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Vice-President</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>As per Article 56.</t>
+          <t>Bound to act as per Article 74 (after 42nd Amendment).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which President was also a freedom fighter and teacher?</t>
+          <t>During President's Rule, the President acts through</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Pranab Mukherjee</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sarvepalli Radhakrishnan</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fakhruddin Ali Ahmed</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarvepalli Radhakrishnan</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2nd President and philosopher.</t>
+          <t>He governs on behalf of President.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>In case of vacancy, who acts as President?</t>
+          <t>President acts on the aid and advice of</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -651,37 +651,37 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vice-President</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Vice-President</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Acts till new President elected.</t>
+          <t>As per Article 74.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>President acts on the aid and advice of</t>
+          <t>In case of vacancy, who acts as President?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -691,3770 +691,3770 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Vice-President</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Vice-President</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>As per Article 74.</t>
+          <t>Acts till new President elected.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>During President's Rule, the President acts through</t>
+          <t>Which President was also a freedom fighter and teacher?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Pranab Mukherjee</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Sarvepalli Radhakrishnan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Fakhruddin Ali Ahmed</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Sarvepalli Radhakrishnan</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>He governs on behalf of President.</t>
+          <t>2nd President and philosopher.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Can President reject advice of Council of Ministers?</t>
+          <t>President gives his resignation to</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yes, in all cases</t>
+          <t>Vice-President</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Only during emergency</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Vice-President</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Bound to act as per Article 74 (after 42nd Amendment).</t>
+          <t>As per Article 56.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What majority is required for impeachment of President?</t>
+          <t>The President can appoint how many members to Rajya Sabha?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Simple</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Absolute</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2/3rd of total membership</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2/3rd of members present and voting</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2/3rd of total membership</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Of both Houses.</t>
+          <t>As per Article 80.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>President is part of</t>
+          <t>Which article deals with the election of the President?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Executive only</t>
+          <t>Article 52</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Parliament only</t>
+          <t>Article 54</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Judiciary only</t>
+          <t>Article 61</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 54</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Along with Lok Sabha and Rajya Sabha.</t>
+          <t>It provides the procedure.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>President's assent to a bill converts it into</t>
+          <t>President’s election can be challenged in</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Act</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ordinance</t>
+          <t>High Court</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Law</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Act</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Law comes into force after assent.</t>
+          <t>As per Article 71.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>President’s address to the Parliament is under</t>
+          <t>Who can initiate impeachment of the President?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Article 72</t>
+          <t>Only Lok Sabha</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Article 86</t>
+          <t>Only Rajya Sabha</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Article 87</t>
+          <t>Either House</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Article 89</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Article 87</t>
+          <t>Either House</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>At the beginning of first session each year.</t>
+          <t>With required majority.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which body does not participate in Presidential election?</t>
+          <t>Which of these is not appointed by the President?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Comptroller and Auditor General</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Chief Election Commissioner</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>State Assemblies</t>
+          <t>Chief Minister</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Legislative Councils</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Legislative Councils</t>
+          <t>Chief Minister</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Only elected MLAs and MPs vote.</t>
+          <t>Appointed by Governor.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Who was the first President of India?</t>
+          <t>Who decides disputes regarding Presidential elections?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>S. Radhakrishnan</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>V.V. Giri</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Only President to serve 2 full terms.</t>
+          <t>Under Article 71.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which Article deals with the election of the President?</t>
+          <t>President’s salary is decided by</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Article 52</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Article 54</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Article 54</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Describes election process.</t>
+          <t>As per Article 125.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>President’s salary is decided by</t>
+          <t>Which Article deals with the election of the President?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Article 52</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 54</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 54</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>As per Article 125.</t>
+          <t>Describes election process.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Who decides disputes regarding Presidential elections?</t>
+          <t>Who was the first President of India?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>S. Radhakrishnan</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>V.V. Giri</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Under Article 71.</t>
+          <t>Only President to serve 2 full terms.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which of these is not appointed by the President?</t>
+          <t>Which body does not participate in Presidential election?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Comptroller and Auditor General</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Chief Election Commissioner</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chief Minister</t>
+          <t>State Assemblies</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Legislative Councils</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chief Minister</t>
+          <t>Legislative Councils</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Appointed by Governor.</t>
+          <t>Only elected MLAs and MPs vote.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Who can initiate impeachment of the President?</t>
+          <t>President’s address to the Parliament is under</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Only Lok Sabha</t>
+          <t>Article 72</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Only Rajya Sabha</t>
+          <t>Article 86</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Either House</t>
+          <t>Article 87</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Article 89</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Either House</t>
+          <t>Article 87</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>With required majority.</t>
+          <t>At the beginning of first session each year.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>President’s election can be challenged in</t>
+          <t>President's assent to a bill converts it into</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Act</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>High Court</t>
+          <t>Ordinance</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Law</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Act</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>As per Article 71.</t>
+          <t>Law comes into force after assent.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The first President of Independent India was</t>
+          <t>Which President served as Vice President before becoming President?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>Sarvepalli Radhakrishnan</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>APJ Abdul Kalam</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Pranab Mukherjee</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>Sarvepalli Radhakrishnan</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Jawaharlal Nehru</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Rajendra Prasad</t>
-        </is>
-      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Served from 1950 to 1962.</t>
+          <t>Vice President from 1952–62.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The President is elected by</t>
+          <t>Term of office of the President is</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>People directly</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MLAs only</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MPs only</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Electoral college</t>
+          <t>Until Parliament decides</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Electoral college</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Includes elected MPs and MLAs.</t>
+          <t>Can be re-elected.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>President can dissolve Lok Sabha on advice of</t>
+          <t>The President of India is elected by</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>People directly</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Lok Sabha only</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Rajya Sabha only</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Electoral college</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Electoral college</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Headed by Prime Minister.</t>
+          <t>Includes MPs and MLAs.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Who administers the oath of office to the President?</t>
+          <t>In which case did Supreme Court define Presidential powers under Article 74?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Golaknath Case</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Kesavananda Bharati Case</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>S.R. Bommai Case</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>Shamsher Singh Case</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Shamsher Singh Case</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>As per tradition and Article 60.</t>
+          <t>Clarified "aid and advice".</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>What is the term of office of the President?</t>
+          <t>President’s rule is imposed under</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Article 352</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Article 360</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Till death</t>
+          <t>Article 370</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Mentioned in Article 56.</t>
+          <t>When state machinery fails.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>President’s rule is imposed under</t>
+          <t>What is the term of office of the President?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Article 352</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Article 360</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Article 370</t>
+          <t>Till death</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>When state machinery fails.</t>
+          <t>Mentioned in Article 56.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>In which case did Supreme Court define Presidential powers under Article 74?</t>
+          <t>Who administers the oath of office to the President?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Golaknath Case</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati Case</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>S.R. Bommai Case</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Shamsher Singh Case</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Shamsher Singh Case</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Clarified "aid and advice".</t>
+          <t>As per tradition and Article 60.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The President of India is elected by</t>
+          <t>President can dissolve Lok Sabha on advice of</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>People directly</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Lok Sabha only</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rajya Sabha only</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Electoral college</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Electoral college</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Includes MPs and MLAs.</t>
+          <t>Headed by Prime Minister.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Term of office of the President is</t>
+          <t>The President is elected by</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>People directly</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>MLAs only</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>MPs only</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Until Parliament decides</t>
+          <t>Electoral college</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Electoral college</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Can be re-elected.</t>
+          <t>Includes elected MPs and MLAs.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which President served as Vice President before becoming President?</t>
+          <t>The first President of Independent India was</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>Zakir Hussain</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>Rajendra Prasad</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Sarvepalli Radhakrishnan</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>APJ Abdul Kalam</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pranab Mukherjee</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarvepalli Radhakrishnan</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Vice President from 1952–62.</t>
+          <t>Served from 1950 to 1962.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>President’s power to grant pardon is under</t>
+          <t>Who was the first woman President of India?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Article 72</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>Sushma Swaraj</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Article 72</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Covers pardon, reprieve, respite etc.</t>
+          <t>Elected in 2007.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>What is the maximum gap allowed between two sessions of Parliament?</t>
+          <t>Which body conducts Presidential elections?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3 months</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4 months</t>
+          <t>Election Commission of India</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>9 months</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Election Commission of India</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>As per Article 85.</t>
+          <t>As per Article 324.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>In case of dispute in Presidential election, which body decides?</t>
+          <t>Impeachment of the President is mentioned in</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 61</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Article 54</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Article 61</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>As per Article 71.</t>
+          <t>Details process and majority needed.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Who is the constitutional head of India?</t>
+          <t>When can the President use veto power?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Any bill</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Money bill</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Finance bill</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Budget bill</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Any bill</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>The President is the nominal executive head.</t>
+          <t>Except money bill in some cases.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Who assists the President in their official duties?</t>
+          <t>Can President's salary be reduced during emergency?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Only by Parliament</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cabinet Secretary</t>
+          <t>Only by Supreme Court</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Headed by Prime Minister.</t>
+          <t>Under Financial Emergency (Article 360).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Can President's salary be reduced during emergency?</t>
+          <t>Who assists the President in their official duties?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Only by Parliament</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Only by Supreme Court</t>
+          <t>Cabinet Secretary</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Under Financial Emergency (Article 360).</t>
+          <t>Headed by Prime Minister.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>When can the President use veto power?</t>
+          <t>Who is the constitutional head of India?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Any bill</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Money bill</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Finance bill</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Budget bill</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Any bill</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Except money bill in some cases.</t>
+          <t>The President is the nominal executive head.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Impeachment of the President is mentioned in</t>
+          <t>In case of dispute in Presidential election, which body decides?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Article 61</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Article 54</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Article 61</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Details process and majority needed.</t>
+          <t>As per Article 71.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which body conducts Presidential elections?</t>
+          <t>What is the maximum gap allowed between two sessions of Parliament?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>3 months</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Election Commission of India</t>
+          <t>4 months</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>9 months</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Election Commission of India</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>As per Article 324.</t>
+          <t>As per Article 85.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Who was the first woman President of India?</t>
+          <t>President’s power to grant pardon is under</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Article 72</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sushma Swaraj</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Article 72</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Elected in 2007.</t>
+          <t>Covers pardon, reprieve, respite etc.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>What is the President's veto power called?</t>
+          <t>President can return a bill to Parliament</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Judicial veto</t>
+          <t>Any number of times</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Executive veto</t>
+          <t>Only once</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Legislative veto</t>
+          <t>Twice</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pocket veto</t>
+          <t>Never</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pocket veto</t>
+          <t>Only once</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Where President takes no action on a bill.</t>
+          <t>If passed again, must give assent.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which President served two terms?</t>
+          <t>Who was the first Sikh President of India?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>Giani Zail Singh</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>R. Venkataraman</t>
+          <t>KR Narayanan</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
+          <t>Pranab Mukherjee</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
           <t>Giani Zail Singh</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Rajendra Prasad</t>
-        </is>
-      </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Only President to serve two terms.</t>
+          <t>Served from 1982–87.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>During vacancy in President's office, election must be held within</t>
+          <t>President can declare Financial Emergency under</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1 month</t>
+          <t>Article 352</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2 months</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Article 360</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>Article 370</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Article 360</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>As per Article 62.</t>
+          <t>If financial stability is threatened.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Who appoints the Prime Minister of India?</t>
+          <t>How many times can one person be elected as President?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Once</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Vice-President</t>
+          <t>Twice</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Thrice</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Any number of times</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Any number of times</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Generally the leader of majority.</t>
+          <t>No limit in Constitution.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The President is the part of</t>
+          <t>Which President was known as the 'Missile Man of India'?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>R. Venkataraman</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>All of these</t>
+          <t>Pranab Mukherjee</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>As per Article 53.</t>
+          <t>11th President, a scientist.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which President was known as the 'Missile Man of India'?</t>
+          <t>The President is the part of</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>R. Venkataraman</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Pranab Mukherjee</t>
+          <t>All of these</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>11th President, a scientist.</t>
+          <t>As per Article 53.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>How many times can one person be elected as President?</t>
+          <t>Who appoints the Prime Minister of India?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Once</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Twice</t>
+          <t>Vice-President</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Thrice</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Any number of times</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Any number of times</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>No limit in Constitution.</t>
+          <t>Generally the leader of majority.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>President can declare Financial Emergency under</t>
+          <t>During vacancy in President's office, election must be held within</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Article 352</t>
+          <t>1 month</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>2 months</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Article 360</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Article 370</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Article 360</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>If financial stability is threatened.</t>
+          <t>As per Article 62.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Who was the first Sikh President of India?</t>
+          <t>Which President served two terms?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>Rajendra Prasad</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>R. Venkataraman</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>Giani Zail Singh</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>KR Narayanan</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Pranab Mukherjee</t>
-        </is>
-      </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Giani Zail Singh</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Served from 1982–87.</t>
+          <t>Only President to serve two terms.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>President can return a bill to Parliament</t>
+          <t>What is the President's veto power called?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Any number of times</t>
+          <t>Judicial veto</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Only once</t>
+          <t>Executive veto</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Twice</t>
+          <t>Legislative veto</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Pocket veto</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Only once</t>
+          <t>Pocket veto</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>If passed again, must give assent.</t>
+          <t>Where President takes no action on a bill.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which house introduces impeachment charges?</t>
+          <t>Which type of bill requires President’s prior recommendation?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Only Lok Sabha</t>
+          <t>Finance Bill</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Only Rajya Sabha</t>
+          <t>Money Bill</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Any House</t>
+          <t>Ordinary Bill</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Private Bill</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Any House</t>
+          <t>Money Bill</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>But with special majority.</t>
+          <t>Introduced only with President's approval.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which emergency needs written recommendation of Cabinet to President?</t>
+          <t>Can a person be President and member of Parliament at the same time?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>President's Rule</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>National Emergency</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Financial Emergency</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
+          <t>Only if nominated</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Only if Speaker</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>National Emergency</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>As per 44th Amendment.</t>
+          <t>Cannot hold both offices.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Who was President during Indo-Pak war of 1971?</t>
+          <t>Which of these is not a discretionary power of President?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>Sending back advice</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Appointing PM</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>V.V. Giri</t>
+          <t>Dismissing CM</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>R. Venkataraman</t>
+          <t>Pocket veto</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>V.V. Giri</t>
+          <t>Dismissing CM</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>In office during war.</t>
+          <t>President must act on aid and advice.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which President started ‘Rashtrapati Bhavan Darshan’?</t>
+          <t>Who was the first President to be elected unopposed?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>Zakir Hussain</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Neelam Sanjiva Reddy</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>Rajendra Prasad</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>APJ Abdul Kalam</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>R. Venkataraman</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Pratibha Patil</t>
-        </is>
-      </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Neelam Sanjiva Reddy</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>To promote public interaction.</t>
+          <t>Elected unopposed in 1977.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>The first Dalit President of India was</t>
+          <t>The salary and allowances of the President are decided by</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>KR Narayanan</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>R Venkataraman</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Giani Zail Singh</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>KR Narayanan</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>10th President of India.</t>
+          <t>As per Article 59.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The salary and allowances of the President are decided by</t>
+          <t>The first Dalit President of India was</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>KR Narayanan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>R Venkataraman</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Giani Zail Singh</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>KR Narayanan</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>As per Article 59.</t>
+          <t>10th President of India.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Who was the first President to be elected unopposed?</t>
+          <t>Which President started ‘Rashtrapati Bhavan Darshan’?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Neelam Sanjiva Reddy</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>R. Venkataraman</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
+          <t>Pratibha Patil</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
           <t>APJ Abdul Kalam</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Neelam Sanjiva Reddy</t>
-        </is>
-      </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Elected unopposed in 1977.</t>
+          <t>To promote public interaction.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which of these is not a discretionary power of President?</t>
+          <t>Who was President during Indo-Pak war of 1971?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sending back advice</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Appointing PM</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dismissing CM</t>
+          <t>V.V. Giri</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pocket veto</t>
+          <t>R. Venkataraman</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dismissing CM</t>
+          <t>V.V. Giri</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>President must act on aid and advice.</t>
+          <t>In office during war.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Can a person be President and member of Parliament at the same time?</t>
+          <t>Which emergency needs written recommendation of Cabinet to President?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>President's Rule</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>National Emergency</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Only if nominated</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Only if Speaker</t>
-        </is>
-      </c>
+          <t>Financial Emergency</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>National Emergency</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Cannot hold both offices.</t>
+          <t>As per 44th Amendment.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which type of bill requires President’s prior recommendation?</t>
+          <t>Which house introduces impeachment charges?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Finance Bill</t>
+          <t>Only Lok Sabha</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Money Bill</t>
+          <t>Only Rajya Sabha</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ordinary Bill</t>
+          <t>Any House</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Private Bill</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Money Bill</t>
+          <t>Any House</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Introduced only with President's approval.</t>
+          <t>But with special majority.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which of these is NOT a judicial power of the President?</t>
+          <t>How is value of vote of an MLA in Presidential election determined?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Pardon</t>
+          <t>Equal to MP</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Reprieve</t>
+          <t>Based on population</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Remission</t>
+          <t>One vote only</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Review of judgment</t>
+          <t>Random allotment</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Review of judgment</t>
+          <t>Based on population</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Done only by courts.</t>
+          <t>Population to MLA ratio of the state.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>President can declare financial emergency under</t>
+          <t>Who is the supreme commander of the armed forces?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Article 352</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>Defense Minister</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Article 360</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Article 365</t>
+          <t>Chief of Defense Staff</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Article 360</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>When financial stability is threatened.</t>
+          <t>As per Article 53.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which President faced impeachment motion?</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>Can President dissolve Rajya Sabha?</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Only with Supreme Court advice</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
+          <t>Only during Emergency</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>No Indian President has been impeached.</t>
+          <t>Rajya Sabha is a permanent house.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>President may not return which type of bill?</t>
+          <t>Which one is not a qualification for becoming President?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ordinary Bill</t>
+          <t>Indian citizen</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Money Bill</t>
+          <t>Completed 35 years</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Constitutional Amendment Bill</t>
+          <t>Member of Parliament</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Finance Bill</t>
+          <t>Qualified to be Lok Sabha member</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Money Bill</t>
+          <t>Member of Parliament</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>No power to return it.</t>
+          <t>Only need eligibility to become one.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>President can appoint which of the following?</t>
+          <t>Which President served during Emergency (1975)?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Zail Singh</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>Fakhruddin Ali Ahmed</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Fakhruddin Ali Ahmed</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>President appoints several constitutional authorities.</t>
+          <t>Signed emergency proclamation in 1975.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which President served during Emergency (1975)?</t>
+          <t>President can appoint which of the following?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Zail Singh</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Fakhruddin Ali Ahmed</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fakhruddin Ali Ahmed</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Signed emergency proclamation in 1975.</t>
+          <t>President appoints several constitutional authorities.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which one is not a qualification for becoming President?</t>
+          <t>President may not return which type of bill?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Indian citizen</t>
+          <t>Ordinary Bill</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Completed 35 years</t>
+          <t>Money Bill</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Member of Parliament</t>
+          <t>Constitutional Amendment Bill</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Qualified to be Lok Sabha member</t>
+          <t>Finance Bill</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Member of Parliament</t>
+          <t>Money Bill</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Only need eligibility to become one.</t>
+          <t>No power to return it.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Can President dissolve Rajya Sabha?</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Which President faced impeachment motion?</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Only with Supreme Court advice</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Only during Emergency</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+          <t>Rajendra Prasad</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Rajya Sabha is a permanent house.</t>
+          <t>No Indian President has been impeached.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Who is the supreme commander of the armed forces?</t>
+          <t>President can declare financial emergency under</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Article 352</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Defense Minister</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 360</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Chief of Defense Staff</t>
+          <t>Article 365</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 360</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>As per Article 53.</t>
+          <t>When financial stability is threatened.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>How is value of vote of an MLA in Presidential election determined?</t>
+          <t>Which of these is NOT a judicial power of the President?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Equal to MP</t>
+          <t>Pardon</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Based on population</t>
+          <t>Reprieve</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>One vote only</t>
+          <t>Remission</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Random allotment</t>
+          <t>Review of judgment</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Based on population</t>
+          <t>Review of judgment</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Population to MLA ratio of the state.</t>
+          <t>Done only by courts.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>President nominates how many members to Rajya Sabha?</t>
+          <t>If the post of Vice President is vacant, who acts as Vice President?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>No one</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>No one</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Experts in art, literature, science &amp; social service.</t>
+          <t>President’s role continues as is.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Who can remove the President before term ends?</t>
+          <t>Ordinance-making power of President is under</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Article 123</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 123</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Through impeachment process.</t>
+          <t>Allows President to make laws when Parliament not in session.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which President served for the shortest term?</t>
+          <t>Which Article empowers President to grant pardons?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>Article 60</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Article 72</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Fakhruddin Ali Ahmed</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pranab Mukherjee</t>
+          <t>Article 102</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Article 72</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Died during term in 1969.</t>
+          <t>Includes pardon, reprieve, respite, remission.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>President gives resignation to</t>
+          <t>Which article states that executive power is vested in President?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Article 53</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Article 60</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Article 70</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Article 53</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>As per Article 56.</t>
+          <t>Power of Union is vested in President.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Who was acting President after Dr. Zakir Hussain’s death?</t>
+          <t>President acts on aid and advice of</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>VV Giri</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Neelam Sanjiva Reddy</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Mohammad Hidayatullah</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Giani Zail Singh</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Mohammad Hidayatullah</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>As Chief Justice of India.</t>
+          <t>Article 74 mandates this.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>President acts on aid and advice of</t>
+          <t>Who was acting President after Dr. Zakir Hussain’s death?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>VV Giri</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Neelam Sanjiva Reddy</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Mohammad Hidayatullah</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Giani Zail Singh</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Mohammad Hidayatullah</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Article 74 mandates this.</t>
+          <t>As Chief Justice of India.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>97</v>
+        <v>63</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Which article states that executive power is vested in President?</t>
+          <t>President gives resignation to</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Article 53</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Article 60</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Article 70</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Article 53</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Power of Union is vested in President.</t>
+          <t>As per Article 56.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Which Article empowers President to grant pardons?</t>
+          <t>Which President served for the shortest term?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Article 60</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Article 72</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Fakhruddin Ali Ahmed</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Article 102</t>
+          <t>Pranab Mukherjee</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Article 72</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Includes pardon, reprieve, respite, remission.</t>
+          <t>Died during term in 1969.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ordinance-making power of President is under</t>
+          <t>Who can remove the President before term ends?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Article 123</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Article 123</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Allows President to make laws when Parliament not in session.</t>
+          <t>Through impeachment process.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>If the post of Vice President is vacant, who acts as Vice President?</t>
+          <t>President nominates how many members to Rajya Sabha?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>No one</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>No one</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>President’s role continues as is.</t>
+          <t>Experts in art, literature, science &amp; social service.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Can the President attend Parliamentary sessions?</t>
+          <t>Minimum age for President of India is</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Yes, always</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Yes, only inaugural</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Yes, but without voting</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Yes, only inaugural</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>President addresses first session each year.</t>
+          <t>Same as for Governor and Vice President.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>President is elected by</t>
+          <t>Who can remove the President for violation of the Constitution?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>First-past-the-post</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Proportional representation</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Simple majority</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lottery system</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Proportional representation</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Single transferable vote.</t>
+          <t>Through impeachment process.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Can a President be re-elected?</t>
+          <t>Which President had the shortest tenure before resignation?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>VV Giri</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Only once</t>
+          <t>R. Venkataraman</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Yes, any number of times</t>
+          <t>Neelam Sanjiva Reddy</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Only twice</t>
+          <t>Dr. Zakir Hussain</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Yes, any number of times</t>
+          <t>VV Giri</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>No limit on re-election.</t>
+          <t>As acting President before election.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Minimum age to contest Presidential election is</t>
+          <t>In case of President's death or resignation, who acts as President?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>30 years</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>35 years</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>40 years</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>25 years</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>35 years</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>As per Article 58.</t>
+          <t>As per Article 65.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>The President can summon Parliament under</t>
+          <t>Can President be re-elected?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Article 85</t>
+          <t>Yes, only once</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Article 123</t>
+          <t>Yes, any number of times</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Article 324</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Only after 5 years gap</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Article 85</t>
+          <t>Yes, any number of times</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>President summons and prorogues Parliament.</t>
+          <t>No restriction in Constitution.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Can President be re-elected?</t>
+          <t>The President can summon Parliament under</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Yes, only once</t>
+          <t>Article 85</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Yes, any number of times</t>
+          <t>Article 123</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Article 324</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Only after 5 years gap</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Yes, any number of times</t>
+          <t>Article 85</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>No restriction in Constitution.</t>
+          <t>President summons and prorogues Parliament.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>In case of President's death or resignation, who acts as President?</t>
+          <t>Minimum age to contest Presidential election is</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>30 years</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>35 years</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>40 years</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>25 years</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>35 years</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>As per Article 65.</t>
+          <t>As per Article 58.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>92</v>
+        <v>11</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Which President had the shortest tenure before resignation?</t>
+          <t>Can a President be re-elected?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>VV Giri</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>R. Venkataraman</t>
+          <t>Only once</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Neelam Sanjiva Reddy</t>
+          <t>Yes, any number of times</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dr. Zakir Hussain</t>
+          <t>Only twice</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>VV Giri</t>
+          <t>Yes, any number of times</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>As acting President before election.</t>
+          <t>No limit on re-election.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Who can remove the President for violation of the Constitution?</t>
+          <t>President is elected by</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>First-past-the-post</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Proportional representation</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Simple majority</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Lottery system</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Proportional representation</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Through impeachment process.</t>
+          <t>Single transferable vote.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Minimum age for President of India is</t>
+          <t>Can the President attend Parliamentary sessions?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>Yes, always</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>Yes, only inaugural</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>Yes, but without voting</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>Yes, only inaugural</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Same as for Governor and Vice President.</t>
+          <t>President addresses first session each year.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which amendment made it mandatory for the Cabinet to advise the President in writing?</t>
+          <t>Who administers oath to the President?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Vice-President</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>73rd Amendment</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Added to ensure accountability.</t>
+          <t>As per Article 60.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Which one is a discretionary power of the President?</t>
+          <t>President can dissolve Lok Sabha under</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dissolving Lok Sabha</t>
+          <t>Article 85</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Appointing PM in hung Parliament</t>
+          <t>Article 75</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ordinance</t>
+          <t>Article 352</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Pardoning</t>
+          <t>Article 368</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Appointing PM in hung Parliament</t>
+          <t>Article 85</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>When no party has clear majority.</t>
+          <t>When advised by Council of Ministers.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Which is not a legislative power of the President?</t>
+          <t>President’s signature is required on</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Summon Parliament</t>
+          <t>Money Bills</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Dissolve Lok Sabha</t>
+          <t>Ordinances</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Give assent to bills</t>
+          <t>Proclamations of Emergency</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vote in Parliament</t>
+          <t>All of these</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Vote in Parliament</t>
+          <t>All of these</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>President doesn't vote.</t>
+          <t>As head of state.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>President can issue ordinances under</t>
+          <t>Which of the following is true about the President’s ordinance power?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Article 352</t>
+          <t>It can be issued anytime</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Article 123</t>
+          <t>It is equal to law</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>It is permanent</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>It bypasses Parliament</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Article 123</t>
+          <t>It is equal to law</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>When Parliament is not in session.</t>
+          <t>But only temporary till Parliament acts.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>The President can promulgate ordinances when</t>
+          <t>The first woman to contest Presidential election in India was</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Parliament is in session</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Only Lok Sabha is not in session</t>
+          <t>Meira Kumar</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Parliament is not in session</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>PM suggests</t>
+          <t>Subhadra Joshi</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Parliament is not in session</t>
+          <t>Subhadra Joshi</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Under Article 123.</t>
+          <t>Contested in 1967.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>The first woman to contest Presidential election in India was</t>
+          <t>The President can promulgate ordinances when</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Parliament is in session</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Meira Kumar</t>
+          <t>Only Lok Sabha is not in session</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Parliament is not in session</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Subhadra Joshi</t>
+          <t>PM suggests</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Subhadra Joshi</t>
+          <t>Parliament is not in session</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Contested in 1967.</t>
+          <t>Under Article 123.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Which of the following is true about the President’s ordinance power?</t>
+          <t>President can issue ordinances under</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>It can be issued anytime</t>
+          <t>Article 352</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>It is equal to law</t>
+          <t>Article 123</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>It is permanent</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>It bypasses Parliament</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>It is equal to law</t>
+          <t>Article 123</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>But only temporary till Parliament acts.</t>
+          <t>When Parliament is not in session.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>President’s signature is required on</t>
+          <t>Which is not a legislative power of the President?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Money Bills</t>
+          <t>Summon Parliament</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Ordinances</t>
+          <t>Dissolve Lok Sabha</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Proclamations of Emergency</t>
+          <t>Give assent to bills</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>All of these</t>
+          <t>Vote in Parliament</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>All of these</t>
+          <t>Vote in Parliament</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>As head of state.</t>
+          <t>President doesn't vote.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>President can dissolve Lok Sabha under</t>
+          <t>Which one is a discretionary power of the President?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Article 85</t>
+          <t>Dissolving Lok Sabha</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Article 75</t>
+          <t>Appointing PM in hung Parliament</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Article 352</t>
+          <t>Ordinance</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Article 368</t>
+          <t>Pardoning</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Article 85</t>
+          <t>Appointing PM in hung Parliament</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>When advised by Council of Ministers.</t>
+          <t>When no party has clear majority.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Who administers oath to the President?</t>
+          <t>Which amendment made it mandatory for the Cabinet to advise the President in writing?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Vice-President</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>73rd Amendment</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>As per Article 60.</t>
+          <t>Added to ensure accountability.</t>
         </is>
       </c>
     </row>

--- a/Data/IP_ThePresident.xlsx
+++ b/Data/IP_ThePresident.xlsx
@@ -472,591 +472,591 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>President is part of</t>
+          <t>Who can initiate impeachment of the President?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Executive only</t>
+          <t>Only Lok Sabha</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Parliament only</t>
+          <t>Only Rajya Sabha</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Judiciary only</t>
+          <t>Either House</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Either House</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Along with Lok Sabha and Rajya Sabha.</t>
+          <t>With required majority.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>What majority is required for impeachment of President?</t>
+          <t>Which President served during Emergency (1975)?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Simple</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Absolute</t>
+          <t>Zail Singh</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2/3rd of total membership</t>
+          <t>Fakhruddin Ali Ahmed</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2/3rd of members present and voting</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2/3rd of total membership</t>
+          <t>Fakhruddin Ali Ahmed</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Of both Houses.</t>
+          <t>Signed emergency proclamation in 1975.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Can President reject advice of Council of Ministers?</t>
+          <t>Which of these is not a discretionary power of President?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sending back advice</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Appointing PM</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yes, in all cases</t>
+          <t>Dismissing CM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Only during emergency</t>
+          <t>Pocket veto</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Dismissing CM</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bound to act as per Article 74 (after 42nd Amendment).</t>
+          <t>President must act on aid and advice.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>During President's Rule, the President acts through</t>
+          <t>President can declare Financial Emergency under</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Article 352</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Article 360</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Article 370</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Article 360</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>He governs on behalf of President.</t>
+          <t>If financial stability is threatened.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>President acts on the aid and advice of</t>
+          <t>Which article states that executive power is vested in President?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Article 53</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Article 60</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Article 70</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Article 53</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>As per Article 74.</t>
+          <t>Power of Union is vested in President.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>In case of vacancy, who acts as President?</t>
+          <t>Who is the constitutional head of India?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Prime Minister</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Chief Justice</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Prime Minister</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Vice-President</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Vice-President</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Acts till new President elected.</t>
+          <t>The President is the nominal executive head.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which President was also a freedom fighter and teacher?</t>
+          <t>What is the President's veto power called?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pranab Mukherjee</t>
+          <t>Judicial veto</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Executive veto</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sarvepalli Radhakrishnan</t>
+          <t>Legislative veto</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fakhruddin Ali Ahmed</t>
+          <t>Pocket veto</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarvepalli Radhakrishnan</t>
+          <t>Pocket veto</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2nd President and philosopher.</t>
+          <t>Where President takes no action on a bill.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>President gives his resignation to</t>
+          <t>Which type of bill requires President’s prior recommendation?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Finance Bill</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Money Bill</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Vice-President</t>
+          <t>Ordinary Bill</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>Private Bill</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Vice-President</t>
+          <t>Money Bill</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>As per Article 56.</t>
+          <t>Introduced only with President's approval.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>78</v>
+        <v>4</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The President can appoint how many members to Rajya Sabha?</t>
+          <t>Which Article deals with the election of the President?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Article 52</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Article 54</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Article 54</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>As per Article 80.</t>
+          <t>Describes election process.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which article deals with the election of the President?</t>
+          <t>What majority is required for impeachment of President?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Article 52</t>
+          <t>Simple</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Article 54</t>
+          <t>Absolute</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Article 61</t>
+          <t>2/3rd of total membership</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>2/3rd of members present and voting</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Article 54</t>
+          <t>2/3rd of total membership</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>It provides the procedure.</t>
+          <t>Of both Houses.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>President’s election can be challenged in</t>
+          <t>President can dissolve Lok Sabha on advice of</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>High Court</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>As per Article 71.</t>
+          <t>Headed by Prime Minister.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Who can initiate impeachment of the President?</t>
+          <t>Which President served as Vice President before becoming President?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Only Lok Sabha</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Only Rajya Sabha</t>
+          <t>Sarvepalli Radhakrishnan</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Either House</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Pranab Mukherjee</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Either House</t>
+          <t>Sarvepalli Radhakrishnan</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>With required majority.</t>
+          <t>Vice President from 1952–62.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which of these is not appointed by the President?</t>
+          <t>Which President served for the shortest term?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Comptroller and Auditor General</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Chief Election Commissioner</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chief Minister</t>
+          <t>Fakhruddin Ali Ahmed</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Pranab Mukherjee</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chief Minister</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Appointed by Governor.</t>
+          <t>Died during term in 1969.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Who decides disputes regarding Presidential elections?</t>
+          <t>President's assent to a bill converts it into</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Act</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Ordinance</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Law</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Act</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Under Article 71.</t>
+          <t>Law comes into force after assent.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>President’s salary is decided by</t>
+          <t>Who can remove the President before term ends?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>Supreme Court</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>Parliament</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Supreme Court</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1066,2099 +1066,2095 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>As per Article 125.</t>
+          <t>Through impeachment process.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which Article deals with the election of the President?</t>
+          <t>President is part of</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Article 52</t>
+          <t>Executive only</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Article 54</t>
+          <t>Parliament only</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Judiciary only</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Article 54</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Describes election process.</t>
+          <t>Along with Lok Sabha and Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Who was the first President of India?</t>
+          <t>President acts on aid and advice of</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>S. Radhakrishnan</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>V.V. Giri</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Only President to serve 2 full terms.</t>
+          <t>Article 74 mandates this.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which body does not participate in Presidential election?</t>
+          <t>What is the maximum gap allowed between two sessions of Parliament?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>3 months</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>4 months</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>State Assemblies</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Legislative Councils</t>
+          <t>9 months</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Legislative Councils</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Only elected MLAs and MPs vote.</t>
+          <t>As per Article 85.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>President’s address to the Parliament is under</t>
+          <t>President nominates how many members to Rajya Sabha?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Article 72</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Article 86</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Article 87</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Article 89</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Article 87</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>At the beginning of first session each year.</t>
+          <t>Experts in art, literature, science &amp; social service.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>President's assent to a bill converts it into</t>
+          <t>Who appoints the Prime Minister of India?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Act</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ordinance</t>
+          <t>Vice-President</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Law</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Act</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Law comes into force after assent.</t>
+          <t>Generally the leader of majority.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which President served as Vice President before becoming President?</t>
+          <t>In case of dispute in Presidential election, which body decides?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sarvepalli Radhakrishnan</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pranab Mukherjee</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarvepalli Radhakrishnan</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Vice President from 1952–62.</t>
+          <t>As per Article 71.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Term of office of the President is</t>
+          <t>Who was President during Indo-Pak war of 1971?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>V.V. Giri</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Until Parliament decides</t>
+          <t>R. Venkataraman</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>V.V. Giri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Can be re-elected.</t>
+          <t>In office during war.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The President of India is elected by</t>
+          <t>President’s power to grant pardon is under</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>People directly</t>
+          <t>Article 72</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Lok Sabha only</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rajya Sabha only</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Electoral college</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Electoral college</t>
+          <t>Article 72</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Includes MPs and MLAs.</t>
+          <t>Covers pardon, reprieve, respite etc.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>In which case did Supreme Court define Presidential powers under Article 74?</t>
+          <t>Which President served two terms?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Golaknath Case</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati Case</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>S.R. Bommai Case</t>
+          <t>R. Venkataraman</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Shamsher Singh Case</t>
+          <t>Giani Zail Singh</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Shamsher Singh Case</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Clarified "aid and advice".</t>
+          <t>Only President to serve two terms.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>President’s rule is imposed under</t>
+          <t>Which of these is NOT a judicial power of the President?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Article 352</t>
+          <t>Pardon</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>Reprieve</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Article 360</t>
+          <t>Remission</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Article 370</t>
+          <t>Review of judgment</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>Review of judgment</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>When state machinery fails.</t>
+          <t>Done only by courts.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>What is the term of office of the President?</t>
+          <t>Who decides disputes regarding Presidential elections?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Till death</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Mentioned in Article 56.</t>
+          <t>Under Article 71.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Who administers the oath of office to the President?</t>
+          <t>President’s election can be challenged in</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>High Court</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>As per tradition and Article 60.</t>
+          <t>As per Article 71.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>President can dissolve Lok Sabha on advice of</t>
+          <t>Which of these is not appointed by the President?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Comptroller and Auditor General</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Chief Election Commissioner</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Chief Minister</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Chief Minister</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Headed by Prime Minister.</t>
+          <t>Appointed by Governor.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The President is elected by</t>
+          <t>Which President was also a freedom fighter and teacher?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>People directly</t>
+          <t>Pranab Mukherjee</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MLAs only</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MPs only</t>
+          <t>Sarvepalli Radhakrishnan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Electoral college</t>
+          <t>Fakhruddin Ali Ahmed</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Electoral college</t>
+          <t>Sarvepalli Radhakrishnan</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Includes elected MPs and MLAs.</t>
+          <t>2nd President and philosopher.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The first President of Independent India was</t>
+          <t>Which President had the shortest tenure before resignation?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>VV Giri</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>R. Venkataraman</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sarvepalli Radhakrishnan</t>
+          <t>Neelam Sanjiva Reddy</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Dr. Zakir Hussain</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>VV Giri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Served from 1950 to 1962.</t>
+          <t>As acting President before election.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Who was the first woman President of India?</t>
+          <t>The President can summon Parliament under</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Article 85</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Article 123</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Article 324</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sushma Swaraj</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Article 85</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Elected in 2007.</t>
+          <t>President summons and prorogues Parliament.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which body conducts Presidential elections?</t>
+          <t>During President's Rule, the President acts through</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Election Commission of India</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Election Commission of India</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>As per Article 324.</t>
+          <t>He governs on behalf of President.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Impeachment of the President is mentioned in</t>
+          <t>What is the term of office of the President?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Article 61</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Article 54</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>Till death</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Article 61</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Details process and majority needed.</t>
+          <t>Mentioned in Article 56.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>When can the President use veto power?</t>
+          <t>Which one is not a qualification for becoming President?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Any bill</t>
+          <t>Indian citizen</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Money bill</t>
+          <t>Completed 35 years</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Finance bill</t>
+          <t>Member of Parliament</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Budget bill</t>
+          <t>Qualified to be Lok Sabha member</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Any bill</t>
+          <t>Member of Parliament</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Except money bill in some cases.</t>
+          <t>Only need eligibility to become one.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Can President's salary be reduced during emergency?</t>
+          <t>Which house introduces impeachment charges?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Only Lok Sabha</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Only Rajya Sabha</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Only by Parliament</t>
+          <t>Any House</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Only by Supreme Court</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Any House</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Under Financial Emergency (Article 360).</t>
+          <t>But with special majority.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Who assists the President in their official duties?</t>
+          <t>The President can appoint how many members to Rajya Sabha?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cabinet Secretary</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Headed by Prime Minister.</t>
+          <t>As per Article 80.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Who is the constitutional head of India?</t>
+          <t>President’s salary is decided by</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>The President is the nominal executive head.</t>
+          <t>As per Article 125.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>In case of dispute in Presidential election, which body decides?</t>
+          <t>President can dissolve Lok Sabha under</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 85</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Article 75</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Article 352</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Article 368</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Article 85</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>As per Article 71.</t>
+          <t>When advised by Council of Ministers.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>What is the maximum gap allowed between two sessions of Parliament?</t>
+          <t>The first Dalit President of India was</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>3 months</t>
+          <t>KR Narayanan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4 months</t>
+          <t>R Venkataraman</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Giani Zail Singh</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>9 months</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>KR Narayanan</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>As per Article 85.</t>
+          <t>10th President of India.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>President’s power to grant pardon is under</t>
+          <t>The President can promulgate ordinances when</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Article 72</t>
+          <t>Parliament is in session</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Only Lok Sabha is not in session</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>Parliament is not in session</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>PM suggests</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Article 72</t>
+          <t>Parliament is not in session</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Covers pardon, reprieve, respite etc.</t>
+          <t>Under Article 123.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>President can return a bill to Parliament</t>
+          <t>President’s rule is imposed under</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Any number of times</t>
+          <t>Article 352</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Only once</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Twice</t>
+          <t>Article 360</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Article 370</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Only once</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>If passed again, must give assent.</t>
+          <t>When state machinery fails.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Who was the first Sikh President of India?</t>
+          <t>President is elected by</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>First-past-the-post</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Giani Zail Singh</t>
+          <t>Proportional representation</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KR Narayanan</t>
+          <t>Simple majority</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Pranab Mukherjee</t>
+          <t>Lottery system</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Giani Zail Singh</t>
+          <t>Proportional representation</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Served from 1982–87.</t>
+          <t>Single transferable vote.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>President can declare Financial Emergency under</t>
+          <t>Which emergency needs written recommendation of Cabinet to President?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Article 352</t>
+          <t>President's Rule</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>National Emergency</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Article 360</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Article 370</t>
-        </is>
-      </c>
+          <t>Financial Emergency</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Article 360</t>
+          <t>National Emergency</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>If financial stability is threatened.</t>
+          <t>As per 44th Amendment.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>How many times can one person be elected as President?</t>
+          <t>Term of office of the President is</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Once</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Twice</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Thrice</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Any number of times</t>
+          <t>Until Parliament decides</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Any number of times</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>No limit in Constitution.</t>
+          <t>Can be re-elected.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which President was known as the 'Missile Man of India'?</t>
+          <t>President can return a bill to Parliament</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Any number of times</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>R. Venkataraman</t>
+          <t>Only once</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Twice</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Pranab Mukherjee</t>
+          <t>Never</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Only once</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>11th President, a scientist.</t>
+          <t>If passed again, must give assent.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>The President is the part of</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Judiciary</t>
-        </is>
-      </c>
+          <t>Which President faced impeachment motion?</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>All of these</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Executive</t>
-        </is>
-      </c>
+          <t>Rajendra Prasad</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>As per Article 53.</t>
+          <t>No Indian President has been impeached.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Who appoints the Prime Minister of India?</t>
+          <t>Who can remove the President for violation of the Constitution?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Vice-President</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Generally the leader of majority.</t>
+          <t>Through impeachment process.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>During vacancy in President's office, election must be held within</t>
+          <t>Which Article empowers President to grant pardons?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1 month</t>
+          <t>Article 60</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2 months</t>
+          <t>Article 72</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>Article 102</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Article 72</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>As per Article 62.</t>
+          <t>Includes pardon, reprieve, respite, remission.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which President served two terms?</t>
+          <t>Who was the first President of India?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>Dr. Rajendra Prasad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>S. Radhakrishnan</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>Zakir Hussain</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Rajendra Prasad</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>R. Venkataraman</t>
-        </is>
-      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Giani Zail Singh</t>
+          <t>V.V. Giri</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Only President to serve two terms.</t>
+          <t>Only President to serve 2 full terms.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>What is the President's veto power called?</t>
+          <t>President can declare financial emergency under</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Judicial veto</t>
+          <t>Article 352</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Executive veto</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Legislative veto</t>
+          <t>Article 360</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Pocket veto</t>
+          <t>Article 365</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pocket veto</t>
+          <t>Article 360</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Where President takes no action on a bill.</t>
+          <t>When financial stability is threatened.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which type of bill requires President’s prior recommendation?</t>
+          <t>Can President reject advice of Council of Ministers?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Finance Bill</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Money Bill</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ordinary Bill</t>
+          <t>Yes, in all cases</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Private Bill</t>
+          <t>Only during emergency</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Money Bill</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Introduced only with President's approval.</t>
+          <t>Bound to act as per Article 74 (after 42nd Amendment).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Can a person be President and member of Parliament at the same time?</t>
+          <t>Which is not a legislative power of the President?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Summon Parliament</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Dissolve Lok Sabha</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Only if nominated</t>
+          <t>Give assent to bills</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Only if Speaker</t>
+          <t>Vote in Parliament</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Vote in Parliament</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Cannot hold both offices.</t>
+          <t>President doesn't vote.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which of these is not a discretionary power of President?</t>
+          <t>Can President's salary be reduced during emergency?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sending back advice</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Appointing PM</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dismissing CM</t>
+          <t>Only by Parliament</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Pocket veto</t>
+          <t>Only by Supreme Court</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dismissing CM</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>President must act on aid and advice.</t>
+          <t>Under Financial Emergency (Article 360).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Who was the first President to be elected unopposed?</t>
+          <t>Which article deals with the election of the President?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Article 52</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Neelam Sanjiva Reddy</t>
+          <t>Article 54</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>Article 61</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neelam Sanjiva Reddy</t>
+          <t>Article 54</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Elected unopposed in 1977.</t>
+          <t>It provides the procedure.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>The salary and allowances of the President are decided by</t>
+          <t>How many times can one person be elected as President?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Once</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Twice</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Thrice</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Any number of times</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Any number of times</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>As per Article 59.</t>
+          <t>No limit in Constitution.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The first Dalit President of India was</t>
+          <t>President can appoint which of the following?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>KR Narayanan</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>R Venkataraman</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Giani Zail Singh</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>KR Narayanan</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>10th President of India.</t>
+          <t>President appoints several constitutional authorities.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which President started ‘Rashtrapati Bhavan Darshan’?</t>
+          <t>Who administers the oath of office to the President?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>R. Venkataraman</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>To promote public interaction.</t>
+          <t>As per tradition and Article 60.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Who was President during Indo-Pak war of 1971?</t>
+          <t>Who was the first woman President of India?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>V.V. Giri</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>R. Venkataraman</t>
+          <t>Sushma Swaraj</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>V.V. Giri</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>In office during war.</t>
+          <t>Elected in 2007.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which emergency needs written recommendation of Cabinet to President?</t>
+          <t>President’s signature is required on</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>President's Rule</t>
+          <t>Money Bills</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>National Emergency</t>
+          <t>Ordinances</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Financial Emergency</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
+          <t>Proclamations of Emergency</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>All of these</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>National Emergency</t>
+          <t>All of these</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>As per 44th Amendment.</t>
+          <t>As head of state.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which house introduces impeachment charges?</t>
+          <t>The salary and allowances of the President are decided by</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Only Lok Sabha</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Only Rajya Sabha</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Any House</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Any House</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>But with special majority.</t>
+          <t>As per Article 59.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>How is value of vote of an MLA in Presidential election determined?</t>
+          <t>Which body does not participate in Presidential election?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Equal to MP</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Based on population</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>One vote only</t>
+          <t>State Assemblies</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Random allotment</t>
+          <t>Legislative Councils</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Based on population</t>
+          <t>Legislative Councils</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Population to MLA ratio of the state.</t>
+          <t>Only elected MLAs and MPs vote.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Who is the supreme commander of the armed forces?</t>
+          <t>Can a person be President and member of Parliament at the same time?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Defense Minister</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Only if nominated</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Chief of Defense Staff</t>
+          <t>Only if Speaker</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>As per Article 53.</t>
+          <t>Cannot hold both offices.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Can President dissolve Rajya Sabha?</t>
+          <t>Who is the supreme commander of the armed forces?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Defense Minister</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Only with Supreme Court advice</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Only during Emergency</t>
+          <t>Chief of Defense Staff</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Rajya Sabha is a permanent house.</t>
+          <t>As per Article 53.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which one is not a qualification for becoming President?</t>
+          <t>Which one is a discretionary power of the President?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Indian citizen</t>
+          <t>Dissolving Lok Sabha</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Completed 35 years</t>
+          <t>Appointing PM in hung Parliament</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Member of Parliament</t>
+          <t>Ordinance</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Qualified to be Lok Sabha member</t>
+          <t>Pardoning</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Member of Parliament</t>
+          <t>Appointing PM in hung Parliament</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Only need eligibility to become one.</t>
+          <t>When no party has clear majority.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which President served during Emergency (1975)?</t>
+          <t>Who was acting President after Dr. Zakir Hussain’s death?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>VV Giri</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Zail Singh</t>
+          <t>Neelam Sanjiva Reddy</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Fakhruddin Ali Ahmed</t>
+          <t>Mohammad Hidayatullah</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Giani Zail Singh</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fakhruddin Ali Ahmed</t>
+          <t>Mohammad Hidayatullah</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Signed emergency proclamation in 1975.</t>
+          <t>As Chief Justice of India.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>President can appoint which of the following?</t>
+          <t>Ordinance-making power of President is under</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Article 123</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Article 123</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>President appoints several constitutional authorities.</t>
+          <t>Allows President to make laws when Parliament not in session.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>President may not return which type of bill?</t>
+          <t>Which amendment made it mandatory for the Cabinet to advise the President in writing?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ordinary Bill</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Money Bill</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Constitutional Amendment Bill</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Finance Bill</t>
+          <t>73rd Amendment</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Money Bill</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>No power to return it.</t>
+          <t>Added to ensure accountability.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which President faced impeachment motion?</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
+          <t>The first woman to contest Presidential election in India was</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Sarojini Naidu</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Meira Kumar</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3168,238 +3164,242 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
+          <t>Subhadra Joshi</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Subhadra Joshi</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>No Indian President has been impeached.</t>
+          <t>Contested in 1967.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>President can declare financial emergency under</t>
+          <t>The President is the part of</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Article 352</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Article 360</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Article 365</t>
+          <t>All of these</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Article 360</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>When financial stability is threatened.</t>
+          <t>As per Article 53.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which of these is NOT a judicial power of the President?</t>
+          <t>Which President was known as the 'Missile Man of India'?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pardon</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Reprieve</t>
+          <t>R. Venkataraman</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Remission</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Review of judgment</t>
+          <t>Pranab Mukherjee</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Review of judgment</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Done only by courts.</t>
+          <t>11th President, a scientist.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>If the post of Vice President is vacant, who acts as Vice President?</t>
+          <t>President’s address to the Parliament is under</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Article 72</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Article 86</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>Article 87</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>No one</t>
+          <t>Article 89</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>No one</t>
+          <t>Article 87</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>President’s role continues as is.</t>
+          <t>At the beginning of first session each year.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ordinance-making power of President is under</t>
+          <t>The President is elected by</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Article 123</t>
+          <t>People directly</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>MLAs only</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>MPs only</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>Electoral college</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Article 123</t>
+          <t>Electoral college</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Allows President to make laws when Parliament not in session.</t>
+          <t>Includes elected MPs and MLAs.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which Article empowers President to grant pardons?</t>
+          <t>Who administers oath to the President?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Article 60</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Article 72</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Vice-President</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Article 102</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Article 72</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Includes pardon, reprieve, respite, remission.</t>
+          <t>As per Article 60.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which article states that executive power is vested in President?</t>
+          <t>President can issue ordinances under</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Article 53</t>
+          <t>Article 352</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Article 60</t>
+          <t>Article 123</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Article 70</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3409,32 +3409,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Article 53</t>
+          <t>Article 123</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Power of Union is vested in President.</t>
+          <t>When Parliament is not in session.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>President acts on aid and advice of</t>
+          <t>President acts on the aid and advice of</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3454,1007 +3454,1007 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Article 74 mandates this.</t>
+          <t>As per Article 74.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Who was acting President after Dr. Zakir Hussain’s death?</t>
+          <t>Can President dissolve Rajya Sabha?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>VV Giri</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Neelam Sanjiva Reddy</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Mohammad Hidayatullah</t>
+          <t>Only with Supreme Court advice</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Giani Zail Singh</t>
+          <t>Only during Emergency</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Mohammad Hidayatullah</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>As Chief Justice of India.</t>
+          <t>Rajya Sabha is a permanent house.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>President gives resignation to</t>
+          <t>Can the President attend Parliamentary sessions?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Yes, always</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Yes, only inaugural</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>Yes, but without voting</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Yes, only inaugural</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>As per Article 56.</t>
+          <t>President addresses first session each year.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Which President served for the shortest term?</t>
+          <t>How is value of vote of an MLA in Presidential election determined?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>Equal to MP</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Based on population</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Fakhruddin Ali Ahmed</t>
+          <t>One vote only</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Pranab Mukherjee</t>
+          <t>Random allotment</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Based on population</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Died during term in 1969.</t>
+          <t>Population to MLA ratio of the state.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Who can remove the President before term ends?</t>
+          <t>Can President be re-elected?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Yes, only once</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Yes, any number of times</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Only after 5 years gap</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Yes, any number of times</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Through impeachment process.</t>
+          <t>No restriction in Constitution.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>President nominates how many members to Rajya Sabha?</t>
+          <t>Impeachment of the President is mentioned in</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Article 61</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Article 54</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Article 61</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Experts in art, literature, science &amp; social service.</t>
+          <t>Details process and majority needed.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Minimum age for President of India is</t>
+          <t>The President of India is elected by</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>People directly</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>Lok Sabha only</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>Rajya Sabha only</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>Electoral college</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>Electoral college</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Same as for Governor and Vice President.</t>
+          <t>Includes MPs and MLAs.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Who can remove the President for violation of the Constitution?</t>
+          <t>If the post of Vice President is vacant, who acts as Vice President?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>No one</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>No one</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Through impeachment process.</t>
+          <t>President’s role continues as is.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Which President had the shortest tenure before resignation?</t>
+          <t>During vacancy in President's office, election must be held within</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>VV Giri</t>
+          <t>1 month</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>R. Venkataraman</t>
+          <t>2 months</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Neelam Sanjiva Reddy</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dr. Zakir Hussain</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>VV Giri</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>As acting President before election.</t>
+          <t>As per Article 62.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>In case of President's death or resignation, who acts as President?</t>
+          <t>Which body conducts Presidential elections?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Election Commission of India</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Election Commission of India</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>As per Article 65.</t>
+          <t>As per Article 324.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Can President be re-elected?</t>
+          <t>Who was the first Sikh President of India?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Yes, only once</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Yes, any number of times</t>
+          <t>Giani Zail Singh</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>KR Narayanan</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Only after 5 years gap</t>
+          <t>Pranab Mukherjee</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Yes, any number of times</t>
+          <t>Giani Zail Singh</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>No restriction in Constitution.</t>
+          <t>Served from 1982–87.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>The President can summon Parliament under</t>
+          <t>President may not return which type of bill?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Article 85</t>
+          <t>Ordinary Bill</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Article 123</t>
+          <t>Money Bill</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Article 324</t>
+          <t>Constitutional Amendment Bill</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Finance Bill</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Article 85</t>
+          <t>Money Bill</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>President summons and prorogues Parliament.</t>
+          <t>No power to return it.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Minimum age to contest Presidential election is</t>
+          <t>In which case did Supreme Court define Presidential powers under Article 74?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>30 years</t>
+          <t>Golaknath Case</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>35 years</t>
+          <t>Kesavananda Bharati Case</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>40 years</t>
+          <t>S.R. Bommai Case</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>25 years</t>
+          <t>Shamsher Singh Case</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>35 years</t>
+          <t>Shamsher Singh Case</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>As per Article 58.</t>
+          <t>Clarified "aid and advice".</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Can a President be re-elected?</t>
+          <t>The first President of Independent India was</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Only once</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Yes, any number of times</t>
+          <t>Sarvepalli Radhakrishnan</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Only twice</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Yes, any number of times</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>No limit on re-election.</t>
+          <t>Served from 1950 to 1962.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>President is elected by</t>
+          <t>When can the President use veto power?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>First-past-the-post</t>
+          <t>Any bill</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Proportional representation</t>
+          <t>Money bill</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Simple majority</t>
+          <t>Finance bill</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lottery system</t>
+          <t>Budget bill</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Proportional representation</t>
+          <t>Any bill</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Single transferable vote.</t>
+          <t>Except money bill in some cases.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Can the President attend Parliamentary sessions?</t>
+          <t>President gives his resignation to</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Yes, always</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Yes, only inaugural</t>
+          <t>Vice-President</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Yes, but without voting</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Yes, only inaugural</t>
+          <t>Vice-President</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>President addresses first session each year.</t>
+          <t>As per Article 56.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Who administers oath to the President?</t>
+          <t>Who was the first President to be elected unopposed?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Neelam Sanjiva Reddy</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Vice-President</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Neelam Sanjiva Reddy</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>As per Article 60.</t>
+          <t>Elected unopposed in 1977.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>President can dissolve Lok Sabha under</t>
+          <t>Which of the following is true about the President’s ordinance power?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Article 85</t>
+          <t>It can be issued anytime</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Article 75</t>
+          <t>It is equal to law</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Article 352</t>
+          <t>It is permanent</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Article 368</t>
+          <t>It bypasses Parliament</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Article 85</t>
+          <t>It is equal to law</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>When advised by Council of Ministers.</t>
+          <t>But only temporary till Parliament acts.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>President’s signature is required on</t>
+          <t>Minimum age to contest Presidential election is</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Money Bills</t>
+          <t>30 years</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Ordinances</t>
+          <t>35 years</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Proclamations of Emergency</t>
+          <t>40 years</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>All of these</t>
+          <t>25 years</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>All of these</t>
+          <t>35 years</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>As head of state.</t>
+          <t>As per Article 58.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which of the following is true about the President’s ordinance power?</t>
+          <t>Who assists the President in their official duties?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>It can be issued anytime</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>It is equal to law</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>It is permanent</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>It bypasses Parliament</t>
+          <t>Cabinet Secretary</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>It is equal to law</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>But only temporary till Parliament acts.</t>
+          <t>Headed by Prime Minister.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>The first woman to contest Presidential election in India was</t>
+          <t>In case of President's death or resignation, who acts as President?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Meira Kumar</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Subhadra Joshi</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Subhadra Joshi</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Contested in 1967.</t>
+          <t>As per Article 65.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>The President can promulgate ordinances when</t>
+          <t>Which President started ‘Rashtrapati Bhavan Darshan’?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Parliament is in session</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Only Lok Sabha is not in session</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Parliament is not in session</t>
+          <t>R. Venkataraman</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>PM suggests</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Parliament is not in session</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Under Article 123.</t>
+          <t>To promote public interaction.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>President can issue ordinances under</t>
+          <t>Minimum age for President of India is</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Article 352</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Article 123</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Article 123</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>When Parliament is not in session.</t>
+          <t>Same as for Governor and Vice President.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Which is not a legislative power of the President?</t>
+          <t>Can a President be re-elected?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Summon Parliament</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Dissolve Lok Sabha</t>
+          <t>Only once</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Give assent to bills</t>
+          <t>Yes, any number of times</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vote in Parliament</t>
+          <t>Only twice</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Vote in Parliament</t>
+          <t>Yes, any number of times</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>President doesn't vote.</t>
+          <t>No limit on re-election.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Which one is a discretionary power of the President?</t>
+          <t>In case of vacancy, who acts as President?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Dissolving Lok Sabha</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Appointing PM in hung Parliament</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ordinance</t>
+          <t>Vice-President</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Pardoning</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Appointing PM in hung Parliament</t>
+          <t>Vice-President</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>When no party has clear majority.</t>
+          <t>Acts till new President elected.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Which amendment made it mandatory for the Cabinet to advise the President in writing?</t>
+          <t>President gives resignation to</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>73rd Amendment</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Added to ensure accountability.</t>
+          <t>As per Article 56.</t>
         </is>
       </c>
     </row>

--- a/Data/IP_ThePresident.xlsx
+++ b/Data/IP_ThePresident.xlsx
@@ -472,3989 +472,3989 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Who can initiate impeachment of the President?</t>
+          <t>Who was the first President to be elected unopposed?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Only Lok Sabha</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Only Rajya Sabha</t>
+          <t>Neelam Sanjiva Reddy</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Either House</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Either House</t>
+          <t>Neelam Sanjiva Reddy</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>With required majority.</t>
+          <t>Elected unopposed in 1977.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which President served during Emergency (1975)?</t>
+          <t>Which of the following is true about the President’s ordinance power?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>It can be issued anytime</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Zail Singh</t>
+          <t>It is equal to law</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fakhruddin Ali Ahmed</t>
+          <t>It is permanent</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>It bypasses Parliament</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fakhruddin Ali Ahmed</t>
+          <t>It is equal to law</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Signed emergency proclamation in 1975.</t>
+          <t>But only temporary till Parliament acts.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which of these is not a discretionary power of President?</t>
+          <t>Minimum age to contest Presidential election is</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sending back advice</t>
+          <t>30 years</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Appointing PM</t>
+          <t>35 years</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dismissing CM</t>
+          <t>40 years</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pocket veto</t>
+          <t>25 years</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dismissing CM</t>
+          <t>35 years</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>President must act on aid and advice.</t>
+          <t>As per Article 58.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>President can declare Financial Emergency under</t>
+          <t>Who assists the President in their official duties?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Article 352</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Article 360</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Article 370</t>
+          <t>Cabinet Secretary</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Article 360</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>If financial stability is threatened.</t>
+          <t>Headed by Prime Minister.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which article states that executive power is vested in President?</t>
+          <t>In case of President's death or resignation, who acts as President?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Article 53</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Article 60</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Article 70</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Article 53</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Power of Union is vested in President.</t>
+          <t>As per Article 65.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Who is the constitutional head of India?</t>
+          <t>Which President started ‘Rashtrapati Bhavan Darshan’?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>R. Venkataraman</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>The President is the nominal executive head.</t>
+          <t>To promote public interaction.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>What is the President's veto power called?</t>
+          <t>Minimum age for President of India is</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Judicial veto</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Executive veto</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Legislative veto</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pocket veto</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pocket veto</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Where President takes no action on a bill.</t>
+          <t>Same as for Governor and Vice President.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which type of bill requires President’s prior recommendation?</t>
+          <t>Can a President be re-elected?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Finance Bill</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Money Bill</t>
+          <t>Only once</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ordinary Bill</t>
+          <t>Yes, any number of times</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Private Bill</t>
+          <t>Only twice</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Money Bill</t>
+          <t>Yes, any number of times</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Introduced only with President's approval.</t>
+          <t>No limit on re-election.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Which Article deals with the election of the President?</t>
+          <t>In case of vacancy, who acts as President?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Article 52</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Article 54</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Vice-President</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Article 54</t>
+          <t>Vice-President</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Describes election process.</t>
+          <t>Acts till new President elected.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>What majority is required for impeachment of President?</t>
+          <t>President gives resignation to</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Simple</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Absolute</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2/3rd of total membership</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2/3rd of members present and voting</t>
+          <t>Speaker of Lok Sabha</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2/3rd of total membership</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Of both Houses.</t>
+          <t>As per Article 56.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>President can dissolve Lok Sabha on advice of</t>
+          <t>The President of India is elected by</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>People directly</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Lok Sabha only</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Rajya Sabha only</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Electoral college</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Electoral college</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Headed by Prime Minister.</t>
+          <t>Includes MPs and MLAs.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which President served as Vice President before becoming President?</t>
+          <t>If the post of Vice President is vacant, who acts as Vice President?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sarvepalli Radhakrishnan</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pranab Mukherjee</t>
+          <t>No one</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarvepalli Radhakrishnan</t>
+          <t>No one</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Vice President from 1952–62.</t>
+          <t>President’s role continues as is.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which President served for the shortest term?</t>
+          <t>During vacancy in President's office, election must be held within</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>1 month</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>2 months</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Fakhruddin Ali Ahmed</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pranab Mukherjee</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Died during term in 1969.</t>
+          <t>As per Article 62.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>President's assent to a bill converts it into</t>
+          <t>Which body conducts Presidential elections?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Act</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ordinance</t>
+          <t>Election Commission of India</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Law</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Act</t>
+          <t>Election Commission of India</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Law comes into force after assent.</t>
+          <t>As per Article 324.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>9</v>
+        <v>95</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Who can remove the President before term ends?</t>
+          <t>Who was the first Sikh President of India?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Manmohan Singh</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Giani Zail Singh</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>KR Narayanan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Pranab Mukherjee</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Giani Zail Singh</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Through impeachment process.</t>
+          <t>Served from 1982–87.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>President is part of</t>
+          <t>President may not return which type of bill?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Executive only</t>
+          <t>Ordinary Bill</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Parliament only</t>
+          <t>Money Bill</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Judiciary only</t>
+          <t>Constitutional Amendment Bill</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Finance Bill</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Money Bill</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Along with Lok Sabha and Rajya Sabha.</t>
+          <t>No power to return it.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>President acts on aid and advice of</t>
+          <t>In which case did Supreme Court define Presidential powers under Article 74?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Golaknath Case</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>Kesavananda Bharati Case</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>S.R. Bommai Case</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Shamsher Singh Case</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Shamsher Singh Case</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Article 74 mandates this.</t>
+          <t>Clarified "aid and advice".</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>What is the maximum gap allowed between two sessions of Parliament?</t>
+          <t>The first President of Independent India was</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3 months</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4 months</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Sarvepalli Radhakrishnan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>9 months</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>As per Article 85.</t>
+          <t>Served from 1950 to 1962.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>President nominates how many members to Rajya Sabha?</t>
+          <t>When can the President use veto power?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Any bill</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Money bill</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Finance bill</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>Budget bill</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Any bill</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Experts in art, literature, science &amp; social service.</t>
+          <t>Except money bill in some cases.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Who appoints the Prime Minister of India?</t>
+          <t>President gives his resignation to</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>Chief Justice</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>Vice-President</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Lok Sabha</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Vice-President</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Generally the leader of majority.</t>
+          <t>As per Article 56.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>In case of dispute in Presidential election, which body decides?</t>
+          <t>President’s address to the Parliament is under</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 72</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Article 86</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Article 87</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Article 89</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Article 87</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>As per Article 71.</t>
+          <t>At the beginning of first session each year.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Who was President during Indo-Pak war of 1971?</t>
+          <t>The President is elected by</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>People directly</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>MLAs only</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>V.V. Giri</t>
+          <t>MPs only</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>R. Venkataraman</t>
+          <t>Electoral college</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>V.V. Giri</t>
+          <t>Electoral college</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>In office during war.</t>
+          <t>Includes elected MPs and MLAs.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>President’s power to grant pardon is under</t>
+          <t>Who administers oath to the President?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Article 72</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Article 74</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>Vice-President</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Article 72</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Covers pardon, reprieve, respite etc.</t>
+          <t>As per Article 60.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which President served two terms?</t>
+          <t>President can issue ordinances under</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Article 352</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>Article 123</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>R. Venkataraman</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Giani Zail Singh</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>Article 123</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Only President to serve two terms.</t>
+          <t>When Parliament is not in session.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which of these is NOT a judicial power of the President?</t>
+          <t>President acts on the aid and advice of</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pardon</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Reprieve</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Remission</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Review of judgment</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Review of judgment</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Done only by courts.</t>
+          <t>As per Article 74.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Who decides disputes regarding Presidential elections?</t>
+          <t>Can President dissolve Rajya Sabha?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Only with Supreme Court advice</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Only during Emergency</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Under Article 71.</t>
+          <t>Rajya Sabha is a permanent house.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>President’s election can be challenged in</t>
+          <t>Can the President attend Parliamentary sessions?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>High Court</t>
+          <t>Yes, always</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Yes, only inaugural</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Yes, but without voting</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Yes, only inaugural</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>As per Article 71.</t>
+          <t>President addresses first session each year.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which of these is not appointed by the President?</t>
+          <t>How is value of vote of an MLA in Presidential election determined?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Comptroller and Auditor General</t>
+          <t>Equal to MP</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Chief Election Commissioner</t>
+          <t>Based on population</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chief Minister</t>
+          <t>One vote only</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Random allotment</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chief Minister</t>
+          <t>Based on population</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Appointed by Governor.</t>
+          <t>Population to MLA ratio of the state.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which President was also a freedom fighter and teacher?</t>
+          <t>Can President be re-elected?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pranab Mukherjee</t>
+          <t>Yes, only once</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Yes, any number of times</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sarvepalli Radhakrishnan</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fakhruddin Ali Ahmed</t>
+          <t>Only after 5 years gap</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarvepalli Radhakrishnan</t>
+          <t>Yes, any number of times</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2nd President and philosopher.</t>
+          <t>No restriction in Constitution.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>92</v>
+        <v>10</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which President had the shortest tenure before resignation?</t>
+          <t>Impeachment of the President is mentioned in</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>VV Giri</t>
+          <t>Article 61</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>R. Venkataraman</t>
+          <t>Article 54</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Neelam Sanjiva Reddy</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dr. Zakir Hussain</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>VV Giri</t>
+          <t>Article 61</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>As acting President before election.</t>
+          <t>Details process and majority needed.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The President can summon Parliament under</t>
+          <t>Which body does not participate in Presidential election?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Article 85</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Article 123</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Article 324</t>
+          <t>State Assemblies</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Legislative Councils</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Article 85</t>
+          <t>Legislative Councils</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>President summons and prorogues Parliament.</t>
+          <t>Only elected MLAs and MPs vote.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>During President's Rule, the President acts through</t>
+          <t>Can a person be President and member of Parliament at the same time?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Only if nominated</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Only if Speaker</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>He governs on behalf of President.</t>
+          <t>Cannot hold both offices.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>What is the term of office of the President?</t>
+          <t>Who is the supreme commander of the armed forces?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Defense Minister</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>President</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Till death</t>
+          <t>Chief of Defense Staff</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Mentioned in Article 56.</t>
+          <t>As per Article 53.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which one is not a qualification for becoming President?</t>
+          <t>Which one is a discretionary power of the President?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Indian citizen</t>
+          <t>Dissolving Lok Sabha</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Completed 35 years</t>
+          <t>Appointing PM in hung Parliament</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Member of Parliament</t>
+          <t>Ordinance</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Qualified to be Lok Sabha member</t>
+          <t>Pardoning</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Member of Parliament</t>
+          <t>Appointing PM in hung Parliament</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Only need eligibility to become one.</t>
+          <t>When no party has clear majority.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which house introduces impeachment charges?</t>
+          <t>Who was acting President after Dr. Zakir Hussain’s death?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Only Lok Sabha</t>
+          <t>VV Giri</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Only Rajya Sabha</t>
+          <t>Neelam Sanjiva Reddy</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Any House</t>
+          <t>Mohammad Hidayatullah</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Giani Zail Singh</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Any House</t>
+          <t>Mohammad Hidayatullah</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>But with special majority.</t>
+          <t>As Chief Justice of India.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The President can appoint how many members to Rajya Sabha?</t>
+          <t>Ordinance-making power of President is under</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Article 123</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Article 124</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>Article 123</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>As per Article 80.</t>
+          <t>Allows President to make laws when Parliament not in session.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>President’s salary is decided by</t>
+          <t>Which amendment made it mandatory for the Cabinet to advise the President in writing?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>42nd Amendment</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>52nd Amendment</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cabinet</t>
+          <t>73rd Amendment</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>44th Amendment</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>As per Article 125.</t>
+          <t>Added to ensure accountability.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>President can dissolve Lok Sabha under</t>
+          <t>The first woman to contest Presidential election in India was</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Article 85</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Article 75</t>
+          <t>Meira Kumar</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Article 352</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Article 368</t>
+          <t>Subhadra Joshi</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Article 85</t>
+          <t>Subhadra Joshi</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>When advised by Council of Ministers.</t>
+          <t>Contested in 1967.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The first Dalit President of India was</t>
+          <t>The President is the part of</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>KR Narayanan</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>R Venkataraman</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Giani Zail Singh</t>
+          <t>Legislature</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>All of these</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>KR Narayanan</t>
+          <t>Executive</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>10th President of India.</t>
+          <t>As per Article 53.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The President can promulgate ordinances when</t>
+          <t>Which President was known as the 'Missile Man of India'?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Parliament is in session</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Only Lok Sabha is not in session</t>
+          <t>R. Venkataraman</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Parliament is not in session</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PM suggests</t>
+          <t>Pranab Mukherjee</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Parliament is not in session</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Under Article 123.</t>
+          <t>11th President, a scientist.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>President’s rule is imposed under</t>
+          <t>Can President reject advice of Council of Ministers?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Article 352</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Article 360</t>
+          <t>Yes, in all cases</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Article 370</t>
+          <t>Only during emergency</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>When state machinery fails.</t>
+          <t>Bound to act as per Article 74 (after 42nd Amendment).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>President is elected by</t>
+          <t>Which is not a legislative power of the President?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>First-past-the-post</t>
+          <t>Summon Parliament</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Proportional representation</t>
+          <t>Dissolve Lok Sabha</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Simple majority</t>
+          <t>Give assent to bills</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lottery system</t>
+          <t>Vote in Parliament</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Proportional representation</t>
+          <t>Vote in Parliament</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Single transferable vote.</t>
+          <t>President doesn't vote.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which emergency needs written recommendation of Cabinet to President?</t>
+          <t>Can President's salary be reduced during emergency?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>President's Rule</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>National Emergency</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Financial Emergency</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
+          <t>Only by Parliament</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Only by Supreme Court</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>National Emergency</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>As per 44th Amendment.</t>
+          <t>Under Financial Emergency (Article 360).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Term of office of the President is</t>
+          <t>Which article deals with the election of the President?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>Article 52</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Article 54</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6 years</t>
+          <t>Article 61</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Until Parliament decides</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>Article 54</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Can be re-elected.</t>
+          <t>It provides the procedure.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>President can return a bill to Parliament</t>
+          <t>How many times can one person be elected as President?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>Once</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Twice</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Thrice</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>Any number of times</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Only once</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Twice</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Only once</t>
+          <t>Any number of times</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>If passed again, must give assent.</t>
+          <t>No limit in Constitution.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which President faced impeachment motion?</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>President can appoint which of the following?</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Chief Justice of India</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Attorney General</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>All of the above</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>All of the above</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>No Indian President has been impeached.</t>
+          <t>President appoints several constitutional authorities.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Who can remove the President for violation of the Constitution?</t>
+          <t>Who administers the oath of office to the President?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Election Commission</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Vice President</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Lok Sabha Speaker</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Through impeachment process.</t>
+          <t>As per tradition and Article 60.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which Article empowers President to grant pardons?</t>
+          <t>Who was the first woman President of India?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Article 60</t>
+          <t>Indira Gandhi</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Article 72</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Article 102</t>
+          <t>Sushma Swaraj</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Article 72</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Includes pardon, reprieve, respite, remission.</t>
+          <t>Elected in 2007.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Who was the first President of India?</t>
+          <t>President’s signature is required on</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>Money Bills</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>S. Radhakrishnan</t>
+          <t>Ordinances</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Proclamations of Emergency</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>V.V. Giri</t>
+          <t>All of these</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dr. Rajendra Prasad</t>
+          <t>All of these</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Only President to serve 2 full terms.</t>
+          <t>As head of state.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>President can declare financial emergency under</t>
+          <t>The salary and allowances of the President are decided by</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Article 352</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Article 360</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Article 365</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Article 360</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>When financial stability is threatened.</t>
+          <t>As per Article 59.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Can President reject advice of Council of Ministers?</t>
+          <t>President’s rule is imposed under</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Article 352</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Yes, in all cases</t>
+          <t>Article 360</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Only during emergency</t>
+          <t>Article 370</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Bound to act as per Article 74 (after 42nd Amendment).</t>
+          <t>When state machinery fails.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which is not a legislative power of the President?</t>
+          <t>President is elected by</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Summon Parliament</t>
+          <t>First-past-the-post</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Dissolve Lok Sabha</t>
+          <t>Proportional representation</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Give assent to bills</t>
+          <t>Simple majority</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vote in Parliament</t>
+          <t>Lottery system</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Vote in Parliament</t>
+          <t>Proportional representation</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>President doesn't vote.</t>
+          <t>Single transferable vote.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Can President's salary be reduced during emergency?</t>
+          <t>Which emergency needs written recommendation of Cabinet to President?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>President's Rule</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>National Emergency</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Only by Parliament</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Only by Supreme Court</t>
-        </is>
-      </c>
+          <t>Financial Emergency</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>National Emergency</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Under Financial Emergency (Article 360).</t>
+          <t>As per 44th Amendment.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which article deals with the election of the President?</t>
+          <t>Term of office of the President is</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Article 52</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Article 54</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Article 61</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Until Parliament decides</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Article 54</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>It provides the procedure.</t>
+          <t>Can be re-elected.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>How many times can one person be elected as President?</t>
+          <t>President can return a bill to Parliament</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Once</t>
+          <t>Any number of times</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t>Only once</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>Twice</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Thrice</t>
-        </is>
-      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Any number of times</t>
+          <t>Never</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Any number of times</t>
+          <t>Only once</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>No limit in Constitution.</t>
+          <t>If passed again, must give assent.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>President can appoint which of the following?</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Chief Justice of India</t>
-        </is>
-      </c>
+          <t>Which President faced impeachment motion?</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Attorney General</t>
+          <t>Pratibha Patil</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>All of the above</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>All of the above</t>
-        </is>
-      </c>
+          <t>Rajendra Prasad</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>President appoints several constitutional authorities.</t>
+          <t>No Indian President has been impeached.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Who administers the oath of office to the President?</t>
+          <t>Who can remove the President for violation of the Constitution?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
+          <t>Supreme Court</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Election Commission</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Parliament</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t>Prime Minister</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Chief Justice of India</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Vice President</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Lok Sabha Speaker</t>
-        </is>
-      </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>As per tradition and Article 60.</t>
+          <t>Through impeachment process.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Who was the first woman President of India?</t>
+          <t>Which Article empowers President to grant pardons?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Indira Gandhi</t>
+          <t>Article 60</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Article 72</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sushma Swaraj</t>
+          <t>Article 102</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Article 72</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Elected in 2007.</t>
+          <t>Includes pardon, reprieve, respite, remission.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>President’s signature is required on</t>
+          <t>Who was the first President of India?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Money Bills</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Ordinances</t>
+          <t>S. Radhakrishnan</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Proclamations of Emergency</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>All of these</t>
+          <t>V.V. Giri</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>All of these</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>As head of state.</t>
+          <t>Only President to serve 2 full terms.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>The salary and allowances of the President are decided by</t>
+          <t>President can declare financial emergency under</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Article 352</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Finance Commission</t>
+          <t>Article 360</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Article 365</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Parliament</t>
+          <t>Article 360</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>As per Article 59.</t>
+          <t>When financial stability is threatened.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which body does not participate in Presidential election?</t>
+          <t>The President can summon Parliament under</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Article 85</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Article 123</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>State Assemblies</t>
+          <t>Article 324</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Legislative Councils</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Legislative Councils</t>
+          <t>Article 85</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Only elected MLAs and MPs vote.</t>
+          <t>President summons and prorogues Parliament.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Can a person be President and member of Parliament at the same time?</t>
+          <t>During President's Rule, the President acts through</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Only if nominated</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Only if Speaker</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Cannot hold both offices.</t>
+          <t>He governs on behalf of President.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>81</v>
+        <v>3</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Who is the supreme commander of the armed forces?</t>
+          <t>What is the term of office of the President?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Defense Minister</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>6 years</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Chief of Defense Staff</t>
+          <t>Till death</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>5 years</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>As per Article 53.</t>
+          <t>Mentioned in Article 56.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which one is a discretionary power of the President?</t>
+          <t>Which one is not a qualification for becoming President?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dissolving Lok Sabha</t>
+          <t>Indian citizen</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Appointing PM in hung Parliament</t>
+          <t>Completed 35 years</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ordinance</t>
+          <t>Member of Parliament</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pardoning</t>
+          <t>Qualified to be Lok Sabha member</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Appointing PM in hung Parliament</t>
+          <t>Member of Parliament</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>When no party has clear majority.</t>
+          <t>Only need eligibility to become one.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Who was acting President after Dr. Zakir Hussain’s death?</t>
+          <t>Which house introduces impeachment charges?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>VV Giri</t>
+          <t>Only Lok Sabha</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Neelam Sanjiva Reddy</t>
+          <t>Only Rajya Sabha</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Mohammad Hidayatullah</t>
+          <t>Any House</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Giani Zail Singh</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Mohammad Hidayatullah</t>
+          <t>Any House</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>As Chief Justice of India.</t>
+          <t>But with special majority.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ordinance-making power of President is under</t>
+          <t>The President can appoint how many members to Rajya Sabha?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Article 123</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Article 124</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Article 356</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Article 123</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Allows President to make laws when Parliament not in session.</t>
+          <t>As per Article 80.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which amendment made it mandatory for the Cabinet to advise the President in writing?</t>
+          <t>President’s salary is decided by</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>42nd Amendment</t>
+          <t>Finance Commission</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>52nd Amendment</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>73rd Amendment</t>
+          <t>Cabinet</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>44th Amendment</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Added to ensure accountability.</t>
+          <t>As per Article 125.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The first woman to contest Presidential election in India was</t>
+          <t>President can dissolve Lok Sabha under</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Article 85</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Meira Kumar</t>
+          <t>Article 75</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Article 352</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Subhadra Joshi</t>
+          <t>Article 368</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Subhadra Joshi</t>
+          <t>Article 85</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Contested in 1967.</t>
+          <t>When advised by Council of Ministers.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The President is the part of</t>
+          <t>The first Dalit President of India was</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Judiciary</t>
+          <t>KR Narayanan</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>R Venkataraman</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Legislature</t>
+          <t>Giani Zail Singh</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>All of these</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Executive</t>
+          <t>KR Narayanan</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>As per Article 53.</t>
+          <t>10th President of India.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which President was known as the 'Missile Man of India'?</t>
+          <t>The President can promulgate ordinances when</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Parliament is in session</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>R. Venkataraman</t>
+          <t>Only Lok Sabha is not in session</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Parliament is not in session</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Pranab Mukherjee</t>
+          <t>PM suggests</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Parliament is not in session</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>11th President, a scientist.</t>
+          <t>Under Article 123.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>President’s address to the Parliament is under</t>
+          <t>In case of dispute in Presidential election, which body decides?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Article 72</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Article 86</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Article 87</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Article 89</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Article 87</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>At the beginning of first session each year.</t>
+          <t>As per Article 71.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The President is elected by</t>
+          <t>Who was President during Indo-Pak war of 1971?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>People directly</t>
+          <t>Dr. Rajendra Prasad</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>MLAs only</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>MPs only</t>
+          <t>V.V. Giri</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Electoral college</t>
+          <t>R. Venkataraman</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Electoral college</t>
+          <t>V.V. Giri</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Includes elected MPs and MLAs.</t>
+          <t>In office during war.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Who administers oath to the President?</t>
+          <t>President’s power to grant pardon is under</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Article 72</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Vice-President</t>
+          <t>Article 76</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Article 72</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>As per Article 60.</t>
+          <t>Covers pardon, reprieve, respite etc.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>President can issue ordinances under</t>
+          <t>Which President served two terms?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Article 352</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Article 123</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>R. Venkataraman</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Article 110</t>
+          <t>Giani Zail Singh</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Article 123</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>When Parliament is not in session.</t>
+          <t>Only President to serve two terms.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>President acts on the aid and advice of</t>
+          <t>Which of these is NOT a judicial power of the President?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Pardon</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Reprieve</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Remission</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Speaker</t>
+          <t>Review of judgment</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Review of judgment</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>As per Article 74.</t>
+          <t>Done only by courts.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>93</v>
+        <v>26</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Can President dissolve Rajya Sabha?</t>
+          <t>Who decides disputes regarding Presidential elections?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Only with Supreme Court advice</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Only during Emergency</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Rajya Sabha is a permanent house.</t>
+          <t>Under Article 71.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Can the President attend Parliamentary sessions?</t>
+          <t>President’s election can be challenged in</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Yes, always</t>
+          <t>High Court</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Yes, only inaugural</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Yes, but without voting</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Yes, only inaugural</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>President addresses first session each year.</t>
+          <t>As per Article 71.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>How is value of vote of an MLA in Presidential election determined?</t>
+          <t>Which of these is not appointed by the President?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Equal to MP</t>
+          <t>Comptroller and Auditor General</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Based on population</t>
+          <t>Chief Election Commissioner</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>One vote only</t>
+          <t>Chief Minister</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Random allotment</t>
+          <t>Chief Justice of India</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Based on population</t>
+          <t>Chief Minister</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Population to MLA ratio of the state.</t>
+          <t>Appointed by Governor.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Can President be re-elected?</t>
+          <t>Which President was also a freedom fighter and teacher?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Yes, only once</t>
+          <t>Pranab Mukherjee</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Yes, any number of times</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sarvepalli Radhakrishnan</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Only after 5 years gap</t>
+          <t>Fakhruddin Ali Ahmed</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Yes, any number of times</t>
+          <t>Sarvepalli Radhakrishnan</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>No restriction in Constitution.</t>
+          <t>2nd President and philosopher.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Impeachment of the President is mentioned in</t>
+          <t>Which President had the shortest tenure before resignation?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Article 61</t>
+          <t>VV Giri</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Article 54</t>
+          <t>R. Venkataraman</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Article 80</t>
+          <t>Neelam Sanjiva Reddy</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Article 76</t>
+          <t>Dr. Zakir Hussain</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Article 61</t>
+          <t>VV Giri</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Details process and majority needed.</t>
+          <t>As acting President before election.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>The President of India is elected by</t>
+          <t>President can dissolve Lok Sabha on advice of</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>People directly</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Lok Sabha only</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Rajya Sabha only</t>
+          <t>Governor</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Electoral college</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Electoral college</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Includes MPs and MLAs.</t>
+          <t>Headed by Prime Minister.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>If the post of Vice President is vacant, who acts as Vice President?</t>
+          <t>Which President served as Vice President before becoming President?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Sarvepalli Radhakrishnan</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>No one</t>
+          <t>Pranab Mukherjee</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>No one</t>
+          <t>Sarvepalli Radhakrishnan</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>President’s role continues as is.</t>
+          <t>Vice President from 1952–62.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>During vacancy in President's office, election must be held within</t>
+          <t>Which President served for the shortest term?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>1 month</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2 months</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Fakhruddin Ali Ahmed</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>Pranab Mukherjee</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>Zakir Hussain</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>As per Article 62.</t>
+          <t>Died during term in 1969.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which body conducts Presidential elections?</t>
+          <t>President's assent to a bill converts it into</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Lok Sabha</t>
+          <t>Act</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Election Commission of India</t>
+          <t>Ordinance</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Supreme Court</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rajya Sabha</t>
+          <t>Law</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Election Commission of India</t>
+          <t>Act</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>As per Article 324.</t>
+          <t>Law comes into force after assent.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>95</v>
+        <v>9</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Who was the first Sikh President of India?</t>
+          <t>Who can remove the President before term ends?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Manmohan Singh</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Giani Zail Singh</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>KR Narayanan</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Pranab Mukherjee</t>
+          <t>Election Commission</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Giani Zail Singh</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Served from 1982–87.</t>
+          <t>Through impeachment process.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>President may not return which type of bill?</t>
+          <t>President is part of</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ordinary Bill</t>
+          <t>Executive only</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Money Bill</t>
+          <t>Parliament only</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Constitutional Amendment Bill</t>
+          <t>Judiciary only</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Finance Bill</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Money Bill</t>
+          <t>Parliament</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>No power to return it.</t>
+          <t>Along with Lok Sabha and Rajya Sabha.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>In which case did Supreme Court define Presidential powers under Article 74?</t>
+          <t>President acts on aid and advice of</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Golaknath Case</t>
+          <t>Lok Sabha</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Kesavananda Bharati Case</t>
+          <t>Judiciary</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>S.R. Bommai Case</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Shamsher Singh Case</t>
+          <t>Rajya Sabha</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Shamsher Singh Case</t>
+          <t>Council of Ministers</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Clarified "aid and advice".</t>
+          <t>Article 74 mandates this.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>The first President of Independent India was</t>
+          <t>What is the maximum gap allowed between two sessions of Parliament?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>3 months</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>4 months</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sarvepalli Radhakrishnan</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>9 months</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>6 months</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Served from 1950 to 1962.</t>
+          <t>As per Article 85.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>When can the President use veto power?</t>
+          <t>President nominates how many members to Rajya Sabha?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Any bill</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Money bill</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Finance bill</t>
+          <t>14</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Budget bill</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Any bill</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Except money bill in some cases.</t>
+          <t>Experts in art, literature, science &amp; social service.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>President gives his resignation to</t>
+          <t>Who appoints the Prime Minister of India?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>President</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t>Vice-President</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Lok Sabha</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
           <t>Chief Justice</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Vice-President</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Lok Sabha Speaker</t>
-        </is>
-      </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Vice-President</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>As per Article 56.</t>
+          <t>Generally the leader of majority.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Who was the first President to be elected unopposed?</t>
+          <t>Who can initiate impeachment of the President?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Zakir Hussain</t>
+          <t>Only Lok Sabha</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Neelam Sanjiva Reddy</t>
+          <t>Only Rajya Sabha</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>Either House</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>Supreme Court</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Neelam Sanjiva Reddy</t>
+          <t>Either House</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Elected unopposed in 1977.</t>
+          <t>With required majority.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Which of the following is true about the President’s ordinance power?</t>
+          <t>Which President served during Emergency (1975)?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>It can be issued anytime</t>
+          <t>Rajendra Prasad</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>It is equal to law</t>
+          <t>Zail Singh</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>It is permanent</t>
+          <t>Fakhruddin Ali Ahmed</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>It bypasses Parliament</t>
+          <t>APJ Abdul Kalam</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>It is equal to law</t>
+          <t>Fakhruddin Ali Ahmed</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>But only temporary till Parliament acts.</t>
+          <t>Signed emergency proclamation in 1975.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Minimum age to contest Presidential election is</t>
+          <t>Which of these is not a discretionary power of President?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>30 years</t>
+          <t>Sending back advice</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>35 years</t>
+          <t>Appointing PM</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>40 years</t>
+          <t>Dismissing CM</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>25 years</t>
+          <t>Pocket veto</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>35 years</t>
+          <t>Dismissing CM</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>As per Article 58.</t>
+          <t>President must act on aid and advice.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Who assists the President in their official duties?</t>
+          <t>President can declare Financial Emergency under</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Governor</t>
+          <t>Article 352</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Article 356</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Article 360</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cabinet Secretary</t>
+          <t>Article 370</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Council of Ministers</t>
+          <t>Article 360</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Headed by Prime Minister.</t>
+          <t>If financial stability is threatened.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>In case of President's death or resignation, who acts as President?</t>
+          <t>Which article states that executive power is vested in President?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chief Justice of India</t>
+          <t>Article 53</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Article 60</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Article 70</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>Article 110</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Article 53</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>As per Article 65.</t>
+          <t>Power of Union is vested in President.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Which President started ‘Rashtrapati Bhavan Darshan’?</t>
+          <t>Who is the constitutional head of India?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Rajendra Prasad</t>
+          <t>Prime Minister</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>President</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>R. Venkataraman</t>
+          <t>Chief Justice</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Pratibha Patil</t>
+          <t>Speaker</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>APJ Abdul Kalam</t>
+          <t>President</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>To promote public interaction.</t>
+          <t>The President is the nominal executive head.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Minimum age for President of India is</t>
+          <t>What is the President's veto power called?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>Judicial veto</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>Executive veto</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>Legislative veto</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>Pocket veto</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>Pocket veto</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Same as for Governor and Vice President.</t>
+          <t>Where President takes no action on a bill.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Can a President be re-elected?</t>
+          <t>Which type of bill requires President’s prior recommendation?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Finance Bill</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Only once</t>
+          <t>Money Bill</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Yes, any number of times</t>
+          <t>Ordinary Bill</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Only twice</t>
+          <t>Private Bill</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Yes, any number of times</t>
+          <t>Money Bill</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>No limit on re-election.</t>
+          <t>Introduced only with President's approval.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>In case of vacancy, who acts as President?</t>
+          <t>Which Article deals with the election of the President?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Article 52</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>Article 54</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Vice-President</t>
+          <t>Article 74</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lok Sabha Speaker</t>
+          <t>Article 80</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Vice-President</t>
+          <t>Article 54</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Acts till new President elected.</t>
+          <t>Describes election process.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>President gives resignation to</t>
+          <t>What majority is required for impeachment of President?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>Simple</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Chief Justice</t>
+          <t>Absolute</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Prime Minister</t>
+          <t>2/3rd of total membership</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Speaker of Lok Sabha</t>
+          <t>2/3rd of members present and voting</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Vice President</t>
+          <t>2/3rd of total membership</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>As per Article 56.</t>
+          <t>Of both Houses.</t>
         </is>
       </c>
     </row>
